--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B8" t="n">
-        <v>57682</v>
+        <v>91472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,24 +1405,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R8" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B9" t="n">
-        <v>91472</v>
+        <v>57682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1521,19 +1516,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R9" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1932,57 +1932,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128593782</v>
+        <v>128592766</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>57679</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575415</v>
+        <v>575425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,69 +2036,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592766</v>
+        <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>57679</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575425</v>
+        <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373803</v>
+        <v>6373844</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,12 +2152,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2834,57 +2834,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128594789</v>
+        <v>128591716</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>95891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575404</v>
+        <v>575425</v>
       </c>
       <c r="R21" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3061,48 +3052,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128591716</v>
+        <v>128593719</v>
       </c>
       <c r="B23" t="n">
-        <v>95891</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575425</v>
+        <v>575407</v>
       </c>
       <c r="R23" t="n">
-        <v>6373803</v>
+        <v>6373854</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,12 +3156,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128593719</v>
+        <v>128594789</v>
       </c>
       <c r="B25" t="n">
         <v>98571</v>
@@ -3308,24 +3308,24 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575407</v>
+        <v>575404</v>
       </c>
       <c r="R25" t="n">
-        <v>6373854</v>
+        <v>6373845</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3379,12 +3379,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3507,57 +3507,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>57679</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R27" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3586,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3596,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3623,53 +3619,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>57679</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R28" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3735,57 +3735,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>91472</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R29" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3814,7 +3805,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3824,7 +3815,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,60 +3830,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>91472</v>
+        <v>98571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R30" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,12 +3946,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4391,53 +4391,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B35" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R35" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4466,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4480,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,69 +4495,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R36" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128591526</v>
+        <v>128594351</v>
       </c>
       <c r="B38" t="n">
         <v>57682</v>
@@ -4771,17 +4771,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575421</v>
+        <v>575496</v>
       </c>
       <c r="R38" t="n">
-        <v>6373766</v>
+        <v>6373918</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4847,7 +4847,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128594351</v>
+        <v>128591526</v>
       </c>
       <c r="B39" t="n">
         <v>57682</v>
@@ -4883,17 +4883,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575496</v>
+        <v>575421</v>
       </c>
       <c r="R39" t="n">
-        <v>6373918</v>
+        <v>6373766</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5075,57 +5075,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128593762</v>
+        <v>128594506</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>79702</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575411</v>
+        <v>575410</v>
       </c>
       <c r="R41" t="n">
-        <v>6373848</v>
+        <v>6373926</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5154,7 +5145,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5164,7 +5155,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5179,12 +5170,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5298,10 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128594506</v>
+        <v>128592340</v>
       </c>
       <c r="B43" t="n">
-        <v>79702</v>
+        <v>57682</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5309,37 +5300,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575410</v>
+        <v>575425</v>
       </c>
       <c r="R43" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5512,53 +5508,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128592340</v>
+        <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575425</v>
+        <v>575411</v>
       </c>
       <c r="R45" t="n">
-        <v>6373803</v>
+        <v>6373848</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,69 +5612,73 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128593944</v>
+        <v>128600928</v>
       </c>
       <c r="B46" t="n">
-        <v>98571</v>
+        <v>5362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>101728</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575453</v>
+        <v>575524</v>
       </c>
       <c r="R46" t="n">
-        <v>6373840</v>
+        <v>6373718</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5703,7 +5707,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5713,7 +5717,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fanns på en liggande grov asplåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,79 +5731,76 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128600928</v>
+        <v>128593944</v>
       </c>
       <c r="B47" t="n">
-        <v>5362</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575524</v>
+        <v>575453</v>
       </c>
       <c r="R47" t="n">
-        <v>6373718</v>
+        <v>6373840</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5823,7 +5829,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5833,12 +5839,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fanns på en liggande grov asplåga</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,51 +5848,50 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>79702</v>
+        <v>96173</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R48" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,45 +5973,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594164</v>
+        <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>56876</v>
+        <v>79702</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575441</v>
+        <v>575489</v>
       </c>
       <c r="R49" t="n">
-        <v>6373840</v>
+        <v>6373908</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6054,11 +6054,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6085,10 +6080,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594598</v>
+        <v>128594164</v>
       </c>
       <c r="B50" t="n">
-        <v>96173</v>
+        <v>56876</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6096,34 +6091,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575422</v>
+        <v>575441</v>
       </c>
       <c r="R50" t="n">
-        <v>6373890</v>
+        <v>6373840</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6166,6 +6161,11 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6527,57 +6527,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128593763</v>
+        <v>128589055</v>
       </c>
       <c r="B54" t="n">
-        <v>98571</v>
+        <v>58055</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575376</v>
+        <v>575467</v>
       </c>
       <c r="R54" t="n">
-        <v>6373829</v>
+        <v>6373701</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6606,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6616,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6631,12 +6627,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6759,53 +6755,57 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128589055</v>
+        <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>58055</v>
+        <v>98571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575467</v>
+        <v>575376</v>
       </c>
       <c r="R56" t="n">
-        <v>6373701</v>
+        <v>6373829</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,22 +6859,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>97448</v>
+        <v>92742</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,46 +6882,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R57" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6950,7 +6945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6955,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6975,22 +6970,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B58" t="n">
-        <v>43950</v>
+        <v>97448</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6998,50 +6993,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R58" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7070,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7080,12 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7094,29 +7080,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B59" t="n">
-        <v>92742</v>
+        <v>43950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7124,41 +7109,50 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R59" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7191,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7206,6 +7205,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7224,42 +7224,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B60" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7268,10 +7264,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R60" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7303,7 +7299,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7309,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7340,38 +7336,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R61" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B8" t="n">
-        <v>91472</v>
+        <v>57682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,19 +1405,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R8" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>57682</v>
+        <v>91472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,24 +1521,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R9" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2834,48 +2834,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128591716</v>
+        <v>128593719</v>
       </c>
       <c r="B21" t="n">
-        <v>95891</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575407</v>
       </c>
       <c r="R21" t="n">
-        <v>6373803</v>
+        <v>6373854</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,19 +2938,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128591105</v>
+        <v>128591743</v>
       </c>
       <c r="B22" t="n">
         <v>98571</v>
@@ -2969,24 +2978,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575470</v>
+        <v>575392</v>
       </c>
       <c r="R22" t="n">
-        <v>6373770</v>
+        <v>6373787</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3015,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,19 +3045,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128593719</v>
+        <v>128594789</v>
       </c>
       <c r="B23" t="n">
         <v>98571</v>
@@ -3085,24 +3090,24 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575407</v>
+        <v>575404</v>
       </c>
       <c r="R23" t="n">
-        <v>6373854</v>
+        <v>6373845</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,19 +3161,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128591743</v>
+        <v>128594429</v>
       </c>
       <c r="B24" t="n">
         <v>98571</v>
@@ -3196,20 +3201,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575392</v>
+        <v>575431</v>
       </c>
       <c r="R24" t="n">
-        <v>6373787</v>
+        <v>6373926</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3238,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,57 +3289,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128594789</v>
+        <v>128591716</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>95891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575404</v>
+        <v>575425</v>
       </c>
       <c r="R25" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3391,7 +3396,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128594429</v>
+        <v>128591105</v>
       </c>
       <c r="B26" t="n">
         <v>98571</v>
@@ -3421,27 +3426,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575431</v>
+        <v>575470</v>
       </c>
       <c r="R26" t="n">
-        <v>6373926</v>
+        <v>6373770</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,65 +3495,69 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B27" t="n">
-        <v>57679</v>
+        <v>98571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R27" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3596,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,57 +3623,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>57679</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R28" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128594457</v>
+        <v>128593162</v>
       </c>
       <c r="B57" t="n">
-        <v>92742</v>
+        <v>97448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,41 +6882,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575490</v>
+        <v>575378</v>
       </c>
       <c r="R57" t="n">
-        <v>6373927</v>
+        <v>6373836</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6945,7 +6950,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6955,7 +6960,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6970,22 +6975,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>97448</v>
+        <v>92742</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,46 +6998,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,12 +7086,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7224,38 +7224,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B60" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7264,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R60" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7299,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7336,42 +7340,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B61" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R61" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128533571</v>
       </c>
       <c r="B3" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128534193</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>128534411</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128548728</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128533348</v>
       </c>
       <c r="B8" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128548722</v>
       </c>
       <c r="B10" t="n">
-        <v>58362</v>
+        <v>58366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>128534744</v>
       </c>
       <c r="B11" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,48 +1825,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128590113</v>
+        <v>128593782</v>
       </c>
       <c r="B12" t="n">
-        <v>79702</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575564</v>
+        <v>575415</v>
       </c>
       <c r="R12" t="n">
-        <v>6373780</v>
+        <v>6373844</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,69 +1929,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592766</v>
+        <v>128590113</v>
       </c>
       <c r="B13" t="n">
-        <v>57679</v>
+        <v>79706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575425</v>
+        <v>575564</v>
       </c>
       <c r="R13" t="n">
-        <v>6373803</v>
+        <v>6373780</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,57 +2048,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128593782</v>
+        <v>128592766</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>57683</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575415</v>
+        <v>575425</v>
       </c>
       <c r="R14" t="n">
-        <v>6373844</v>
+        <v>6373803</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,12 +2152,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
         <v>128593286</v>
       </c>
       <c r="B15" t="n">
-        <v>58362</v>
+        <v>58366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96859</v>
+        <v>96865</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128591846</v>
       </c>
       <c r="B18" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>128589508</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>128593153</v>
       </c>
       <c r="B20" t="n">
-        <v>96173</v>
+        <v>96179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2834,57 +2834,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128593719</v>
+        <v>128591716</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>95897</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575407</v>
+        <v>575425</v>
       </c>
       <c r="R21" t="n">
-        <v>6373854</v>
+        <v>6373803</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2913,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2929,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128591743</v>
+        <v>128593719</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2978,20 +2969,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575392</v>
+        <v>575407</v>
       </c>
       <c r="R22" t="n">
-        <v>6373787</v>
+        <v>6373854</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594789</v>
+        <v>128594429</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,27 +3087,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575404</v>
+        <v>575431</v>
       </c>
       <c r="R23" t="n">
-        <v>6373845</v>
+        <v>6373926</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,22 +3161,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128594429</v>
+        <v>128594789</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575431</v>
+        <v>575404</v>
       </c>
       <c r="R24" t="n">
-        <v>6373926</v>
+        <v>6373845</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,60 +3277,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591716</v>
+        <v>128591743</v>
       </c>
       <c r="B25" t="n">
-        <v>95891</v>
+        <v>98579</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575425</v>
+        <v>575392</v>
       </c>
       <c r="R25" t="n">
-        <v>6373803</v>
+        <v>6373787</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,12 +3384,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
         <v>128591105</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3507,57 +3507,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>57683</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R27" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3586,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3596,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3623,53 +3619,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>57679</v>
+        <v>98579</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R28" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3735,48 +3735,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B29" t="n">
-        <v>91472</v>
+        <v>98579</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R29" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3805,7 +3814,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3815,7 +3824,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,69 +3839,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B30" t="n">
-        <v>98571</v>
+        <v>91478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R30" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,12 +3946,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3961,7 +3961,7 @@
         <v>128592258</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128594827</v>
       </c>
       <c r="B32" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96173</v>
+        <v>96179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96173</v>
+        <v>96179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,57 +4391,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>57686</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R35" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4470,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,65 +4491,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B36" t="n">
-        <v>57682</v>
+        <v>98579</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R36" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96173</v>
+        <v>96179</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>128594351</v>
       </c>
       <c r="B38" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>128591526</v>
       </c>
       <c r="B39" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>128594506</v>
       </c>
       <c r="B41" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>128594384</v>
       </c>
       <c r="B42" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>128592340</v>
       </c>
       <c r="B43" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,61 +5624,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128600928</v>
+        <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>5362</v>
+        <v>98579</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575524</v>
+        <v>575453</v>
       </c>
       <c r="R46" t="n">
-        <v>6373718</v>
+        <v>6373840</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5707,7 +5703,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5717,12 +5713,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Fanns på en liggande grov asplåga</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5731,76 +5722,79 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128593944</v>
+        <v>128600928</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>5362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>101728</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575453</v>
+        <v>575524</v>
       </c>
       <c r="R47" t="n">
-        <v>6373840</v>
+        <v>6373718</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5829,7 +5823,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5839,7 +5833,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fanns på en liggande grov asplåga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5848,28 +5847,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594598</v>
+        <v>128594164</v>
       </c>
       <c r="B48" t="n">
-        <v>96173</v>
+        <v>56880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5877,34 +5877,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575422</v>
+        <v>575441</v>
       </c>
       <c r="R48" t="n">
-        <v>6373890</v>
+        <v>6373840</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5947,6 +5947,11 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5973,32 +5978,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B49" t="n">
-        <v>79702</v>
+        <v>96179</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6008,10 +6013,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R49" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6080,45 +6085,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594164</v>
+        <v>128594199</v>
       </c>
       <c r="B50" t="n">
-        <v>56876</v>
+        <v>79706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575441</v>
+        <v>575489</v>
       </c>
       <c r="R50" t="n">
-        <v>6373840</v>
+        <v>6373908</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6161,11 +6166,6 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6195,7 +6195,7 @@
         <v>128593352</v>
       </c>
       <c r="B51" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105609</v>
+        <v>105621</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>128593706</v>
       </c>
       <c r="B53" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>128589055</v>
       </c>
       <c r="B54" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128593162</v>
+        <v>128601004</v>
       </c>
       <c r="B57" t="n">
-        <v>97448</v>
+        <v>43952</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,46 +6882,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>101735</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>6373836</v>
+        <v>6373840</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6950,7 +6954,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6964,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6969,18 +6978,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6990,7 +7000,7 @@
         <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7098,10 +7108,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B59" t="n">
-        <v>43950</v>
+        <v>97454</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7109,50 +7119,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R59" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7205,61 +7206,56 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B60" t="n">
-        <v>98571</v>
+        <v>57686</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7268,10 +7264,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R60" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7303,7 +7299,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7309,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7340,38 +7336,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>57682</v>
+        <v>98579</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R61" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,24 +1405,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R8" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B9" t="n">
-        <v>91478</v>
+        <v>57686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1521,19 +1516,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R9" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1825,57 +1825,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128593782</v>
+        <v>128590113</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>79706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575415</v>
+        <v>575564</v>
       </c>
       <c r="R12" t="n">
-        <v>6373844</v>
+        <v>6373780</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,60 +1920,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128590113</v>
+        <v>128592766</v>
       </c>
       <c r="B13" t="n">
-        <v>79706</v>
+        <v>57683</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575564</v>
+        <v>575425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373780</v>
+        <v>6373803</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,57 +2048,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592766</v>
+        <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>57683</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575425</v>
+        <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373803</v>
+        <v>6373845</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,12 +2152,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
         <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,53 +2499,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128591846</v>
+        <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>57686</v>
+        <v>96185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575382</v>
+        <v>575401</v>
       </c>
       <c r="R18" t="n">
-        <v>6373783</v>
+        <v>6373830</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2574,7 +2569,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2579,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,19 +2594,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128589508</v>
+        <v>128591846</v>
       </c>
       <c r="B19" t="n">
         <v>57686</v>
@@ -2639,11 +2634,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2651,17 +2642,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575483</v>
+        <v>575382</v>
       </c>
       <c r="R19" t="n">
-        <v>6373688</v>
+        <v>6373783</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2690,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,57 +2706,66 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128593153</v>
+        <v>128589508</v>
       </c>
       <c r="B20" t="n">
-        <v>96179</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575401</v>
+        <v>575483</v>
       </c>
       <c r="R20" t="n">
-        <v>6373830</v>
+        <v>6373688</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,7 +2837,7 @@
         <v>128591716</v>
       </c>
       <c r="B21" t="n">
-        <v>95897</v>
+        <v>95903</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128593719</v>
+        <v>128591105</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,27 +2971,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575407</v>
+        <v>575470</v>
       </c>
       <c r="R22" t="n">
-        <v>6373854</v>
+        <v>6373770</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,22 +3040,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594429</v>
+        <v>128593719</v>
       </c>
       <c r="B23" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3082,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3101,13 +3096,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575431</v>
+        <v>575407</v>
       </c>
       <c r="R23" t="n">
-        <v>6373926</v>
+        <v>6373854</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3136,7 +3131,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3141,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,10 +3168,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128594789</v>
+        <v>128591743</v>
       </c>
       <c r="B24" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,29 +3196,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575404</v>
+        <v>575392</v>
       </c>
       <c r="R24" t="n">
-        <v>6373845</v>
+        <v>6373787</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,22 +3263,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591743</v>
+        <v>128594789</v>
       </c>
       <c r="B25" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,20 +3303,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575392</v>
+        <v>575404</v>
       </c>
       <c r="R25" t="n">
-        <v>6373787</v>
+        <v>6373845</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3364,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,22 +3379,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591105</v>
+        <v>128594429</v>
       </c>
       <c r="B26" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,22 +3421,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575470</v>
+        <v>575431</v>
       </c>
       <c r="R26" t="n">
-        <v>6373770</v>
+        <v>6373926</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,12 +3495,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3622,7 +3622,7 @@
         <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,57 +3735,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>98579</v>
+        <v>91484</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R29" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3814,7 +3805,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3824,7 +3815,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,60 +3830,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>91478</v>
+        <v>98585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R30" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,57 +3946,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B31" t="n">
-        <v>98579</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R31" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,50 +4070,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>57686</v>
+        <v>98585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R32" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,53 +4391,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B35" t="n">
-        <v>57686</v>
+        <v>98585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R35" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4466,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4480,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,69 +4495,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B36" t="n">
-        <v>98579</v>
+        <v>57686</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R36" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>128594598</v>
       </c>
       <c r="B49" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128601004</v>
+        <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>43952</v>
+        <v>92754</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,50 +6882,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101735</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575490</v>
       </c>
       <c r="R57" t="n">
-        <v>6373840</v>
+        <v>6373927</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6954,7 +6945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6964,12 +6955,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,7 +6964,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6997,10 +6982,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B58" t="n">
-        <v>92748</v>
+        <v>43952</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7008,41 +6993,50 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7071,7 +7065,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7075,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7090,6 +7089,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>128593162</v>
       </c>
       <c r="B59" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -2164,53 +2164,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B15" t="n">
-        <v>58366</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R15" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,69 +2268,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>58366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R16" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3958,50 +3958,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>98585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R31" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4033,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,45 +4065,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B32" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R32" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5075,48 +5075,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594506</v>
+        <v>128594618</v>
       </c>
       <c r="B41" t="n">
-        <v>79706</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575410</v>
+        <v>575433</v>
       </c>
       <c r="R41" t="n">
-        <v>6373926</v>
+        <v>6373862</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,60 +5170,69 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594384</v>
+        <v>128593762</v>
       </c>
       <c r="B42" t="n">
-        <v>79706</v>
+        <v>98585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575490</v>
+        <v>575411</v>
       </c>
       <c r="R42" t="n">
-        <v>6373927</v>
+        <v>6373848</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5252,7 +5261,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5271,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5277,22 +5286,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128592340</v>
+        <v>128594506</v>
       </c>
       <c r="B43" t="n">
-        <v>57686</v>
+        <v>79706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,42 +5309,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575425</v>
+        <v>575410</v>
       </c>
       <c r="R43" t="n">
-        <v>6373803</v>
+        <v>6373926</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5401,48 +5405,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128594618</v>
+        <v>128594384</v>
       </c>
       <c r="B44" t="n">
-        <v>98585</v>
+        <v>79706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575433</v>
+        <v>575490</v>
       </c>
       <c r="R44" t="n">
-        <v>6373862</v>
+        <v>6373927</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5471,7 +5475,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5481,7 +5485,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,69 +5500,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128593762</v>
+        <v>128592340</v>
       </c>
       <c r="B45" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575411</v>
+        <v>575425</v>
       </c>
       <c r="R45" t="n">
-        <v>6373848</v>
+        <v>6373803</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128534916</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>128534744</v>
       </c>
       <c r="B11" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128590113</v>
       </c>
       <c r="B12" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,57 +1932,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592766</v>
+        <v>128593782</v>
       </c>
       <c r="B13" t="n">
-        <v>57683</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575425</v>
+        <v>575415</v>
       </c>
       <c r="R13" t="n">
-        <v>6373803</v>
+        <v>6373845</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,69 +2036,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128593782</v>
+        <v>128592766</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>57683</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575415</v>
+        <v>575425</v>
       </c>
       <c r="R14" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,69 +2152,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>58366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R15" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,65 +2264,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>58366</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R16" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96871</v>
+        <v>96873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2834,48 +2834,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128591716</v>
+        <v>128593719</v>
       </c>
       <c r="B21" t="n">
-        <v>95903</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575407</v>
       </c>
       <c r="R21" t="n">
-        <v>6373803</v>
+        <v>6373854</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,22 +2938,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128591105</v>
+        <v>128594429</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,22 +2980,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575470</v>
+        <v>575431</v>
       </c>
       <c r="R22" t="n">
-        <v>6373770</v>
+        <v>6373926</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3015,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,22 +3054,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128593719</v>
+        <v>128594789</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,24 +3099,24 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575407</v>
+        <v>575404</v>
       </c>
       <c r="R23" t="n">
-        <v>6373854</v>
+        <v>6373845</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,12 +3170,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3171,7 +3185,7 @@
         <v>128591743</v>
       </c>
       <c r="B24" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,10 +3289,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128594789</v>
+        <v>128591105</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,12 +3319,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3319,13 +3328,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575404</v>
+        <v>575470</v>
       </c>
       <c r="R25" t="n">
-        <v>6373845</v>
+        <v>6373770</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3391,57 +3400,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128594429</v>
+        <v>128591716</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>95905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575431</v>
+        <v>575425</v>
       </c>
       <c r="R26" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,12 +3495,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3622,7 +3622,7 @@
         <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3958,45 +3958,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B31" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R31" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,50 +4070,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>57686</v>
+        <v>98588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R32" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>128594570</v>
       </c>
       <c r="B35" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,48 +5075,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594618</v>
+        <v>128594506</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>79708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575433</v>
+        <v>575410</v>
       </c>
       <c r="R41" t="n">
-        <v>6373862</v>
+        <v>6373926</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,69 +5170,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128593762</v>
+        <v>128594384</v>
       </c>
       <c r="B42" t="n">
-        <v>98585</v>
+        <v>79708</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575411</v>
+        <v>575490</v>
       </c>
       <c r="R42" t="n">
-        <v>6373848</v>
+        <v>6373927</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5261,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5271,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5286,22 +5277,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128594506</v>
+        <v>128592340</v>
       </c>
       <c r="B43" t="n">
-        <v>79706</v>
+        <v>57686</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5309,37 +5300,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575410</v>
+        <v>575425</v>
       </c>
       <c r="R43" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5405,48 +5401,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128594384</v>
+        <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>79706</v>
+        <v>98588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575490</v>
+        <v>575433</v>
       </c>
       <c r="R44" t="n">
-        <v>6373927</v>
+        <v>6373862</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5475,7 +5471,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5485,7 +5481,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5500,65 +5496,69 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128592340</v>
+        <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>57686</v>
+        <v>98588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575425</v>
+        <v>575411</v>
       </c>
       <c r="R45" t="n">
-        <v>6373803</v>
+        <v>6373848</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5866,10 +5866,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594164</v>
+        <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>56880</v>
+        <v>96187</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5877,34 +5877,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575441</v>
+        <v>575422</v>
       </c>
       <c r="R48" t="n">
-        <v>6373840</v>
+        <v>6373890</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5947,11 +5947,6 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5978,32 +5973,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594598</v>
+        <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>96185</v>
+        <v>79708</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6013,10 +6008,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575422</v>
+        <v>575489</v>
       </c>
       <c r="R49" t="n">
-        <v>6373890</v>
+        <v>6373908</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6085,45 +6080,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594199</v>
+        <v>128594164</v>
       </c>
       <c r="B50" t="n">
-        <v>79706</v>
+        <v>56880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575489</v>
+        <v>575441</v>
       </c>
       <c r="R50" t="n">
-        <v>6373908</v>
+        <v>6373840</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6166,6 +6161,11 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6195,7 +6195,7 @@
         <v>128593352</v>
       </c>
       <c r="B51" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B53" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R53" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,27 +6527,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128589055</v>
+        <v>128593706</v>
       </c>
       <c r="B54" t="n">
-        <v>58059</v>
+        <v>57686</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6558,22 +6558,22 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575467</v>
+        <v>575366</v>
       </c>
       <c r="R54" t="n">
-        <v>6373701</v>
+        <v>6373838</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6642,7 +6642,7 @@
         <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6982,10 +6982,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B58" t="n">
-        <v>43952</v>
+        <v>97462</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,50 +6993,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R58" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7065,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7075,12 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7089,29 +7080,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128593162</v>
+        <v>128601004</v>
       </c>
       <c r="B59" t="n">
-        <v>97460</v>
+        <v>43952</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7119,46 +7109,50 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>101735</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R59" t="n">
-        <v>6373836</v>
+        <v>6373840</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7191,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7206,18 +7205,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7339,7 +7339,7 @@
         <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7449,6 +7449,1042 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128741110</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>575558</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6373455</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128740640</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>575577</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6373363</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128739848</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>575504</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6373514</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128740165</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>575530</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6373495</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128741243</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>575561</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6373437</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128741002</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>575568</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6373423</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128740282</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>575535</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6373474</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128739569</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>575460</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6373597</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128740227</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>575537</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6373468</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1932,57 +1932,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128593782</v>
+        <v>128592766</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>57683</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575415</v>
+        <v>575425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,69 +2036,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592766</v>
+        <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>57683</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575425</v>
+        <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373803</v>
+        <v>6373844</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,65 +2152,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B15" t="n">
-        <v>58366</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R15" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,69 +2268,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>58366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R16" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2499,48 +2499,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128593153</v>
+        <v>128591846</v>
       </c>
       <c r="B18" t="n">
-        <v>96187</v>
+        <v>57686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575401</v>
+        <v>575382</v>
       </c>
       <c r="R18" t="n">
-        <v>6373830</v>
+        <v>6373783</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2569,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2579,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,19 +2599,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128591846</v>
+        <v>128589508</v>
       </c>
       <c r="B19" t="n">
         <v>57686</v>
@@ -2634,7 +2639,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2642,17 +2651,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575382</v>
+        <v>575483</v>
       </c>
       <c r="R19" t="n">
-        <v>6373783</v>
+        <v>6373688</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,66 +2715,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128589508</v>
+        <v>128593153</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>96187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575483</v>
+        <v>575401</v>
       </c>
       <c r="R20" t="n">
-        <v>6373688</v>
+        <v>6373830</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,57 +2834,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128593719</v>
+        <v>128591716</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>95905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575407</v>
+        <v>575425</v>
       </c>
       <c r="R21" t="n">
-        <v>6373854</v>
+        <v>6373803</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2913,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2929,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128594429</v>
+        <v>128593719</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2971,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2994,13 +2985,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575431</v>
+        <v>575407</v>
       </c>
       <c r="R22" t="n">
-        <v>6373926</v>
+        <v>6373854</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3029,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594789</v>
+        <v>128594429</v>
       </c>
       <c r="B23" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,27 +3087,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575404</v>
+        <v>575431</v>
       </c>
       <c r="R23" t="n">
-        <v>6373845</v>
+        <v>6373926</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3145,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,22 +3161,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128591743</v>
+        <v>128594789</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,20 +3201,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575392</v>
+        <v>575404</v>
       </c>
       <c r="R24" t="n">
-        <v>6373787</v>
+        <v>6373845</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,22 +3277,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591105</v>
+        <v>128591743</v>
       </c>
       <c r="B25" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,24 +3317,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575470</v>
+        <v>575392</v>
       </c>
       <c r="R25" t="n">
-        <v>6373770</v>
+        <v>6373787</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3373,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,57 +3384,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591716</v>
+        <v>128591105</v>
       </c>
       <c r="B26" t="n">
-        <v>95905</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575425</v>
+        <v>575470</v>
       </c>
       <c r="R26" t="n">
-        <v>6373803</v>
+        <v>6373770</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,53 +3507,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B27" t="n">
-        <v>57683</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R27" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3596,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,57 +3623,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B28" t="n">
-        <v>98588</v>
+        <v>57683</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R28" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3845,7 +3845,7 @@
         <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4391,57 +4391,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B35" t="n">
-        <v>98588</v>
+        <v>57686</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R35" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4470,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,65 +4491,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B36" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R36" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594598</v>
+        <v>128594199</v>
       </c>
       <c r="B48" t="n">
-        <v>96187</v>
+        <v>79708</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575422</v>
+        <v>575489</v>
       </c>
       <c r="R48" t="n">
-        <v>6373890</v>
+        <v>6373908</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,45 +5973,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594199</v>
+        <v>128594164</v>
       </c>
       <c r="B49" t="n">
-        <v>79708</v>
+        <v>56880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575489</v>
+        <v>575441</v>
       </c>
       <c r="R49" t="n">
-        <v>6373908</v>
+        <v>6373840</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6054,6 +6054,11 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6080,10 +6085,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594164</v>
+        <v>128594598</v>
       </c>
       <c r="B50" t="n">
-        <v>56880</v>
+        <v>96187</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6091,34 +6096,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575441</v>
+        <v>575422</v>
       </c>
       <c r="R50" t="n">
-        <v>6373840</v>
+        <v>6373890</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6161,11 +6166,6 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6527,53 +6527,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128593706</v>
+        <v>128593763</v>
       </c>
       <c r="B54" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575366</v>
+        <v>575376</v>
       </c>
       <c r="R54" t="n">
-        <v>6373838</v>
+        <v>6373829</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6606,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6616,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6627,69 +6631,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128594919</v>
+        <v>128593706</v>
       </c>
       <c r="B55" t="n">
-        <v>98588</v>
+        <v>57686</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575407</v>
+        <v>575366</v>
       </c>
       <c r="R55" t="n">
-        <v>6373799</v>
+        <v>6373838</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6755,10 +6755,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128593763</v>
+        <v>128594919</v>
       </c>
       <c r="B56" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6788,24 +6788,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575376</v>
+        <v>575407</v>
       </c>
       <c r="R56" t="n">
-        <v>6373829</v>
+        <v>6373799</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,12 +6859,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7224,38 +7224,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B60" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7264,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R60" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7299,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7336,42 +7340,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B61" t="n">
-        <v>98588</v>
+        <v>57686</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R61" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B8" t="n">
-        <v>91486</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,19 +1405,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R8" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>57686</v>
+        <v>91486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,24 +1521,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R9" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2834,48 +2834,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128591716</v>
+        <v>128593719</v>
       </c>
       <c r="B21" t="n">
-        <v>95905</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575407</v>
       </c>
       <c r="R21" t="n">
-        <v>6373803</v>
+        <v>6373854</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,19 +2938,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128593719</v>
+        <v>128594429</v>
       </c>
       <c r="B22" t="n">
         <v>98591</v>
@@ -2971,7 +2980,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2985,13 +2994,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575407</v>
+        <v>575431</v>
       </c>
       <c r="R22" t="n">
-        <v>6373854</v>
+        <v>6373926</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,7 +3066,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594429</v>
+        <v>128594789</v>
       </c>
       <c r="B23" t="n">
         <v>98591</v>
@@ -3087,27 +3096,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575431</v>
+        <v>575404</v>
       </c>
       <c r="R23" t="n">
-        <v>6373926</v>
+        <v>6373845</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3136,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,19 +3170,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128594789</v>
+        <v>128591743</v>
       </c>
       <c r="B24" t="n">
         <v>98591</v>
@@ -3201,29 +3210,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575404</v>
+        <v>575392</v>
       </c>
       <c r="R24" t="n">
-        <v>6373845</v>
+        <v>6373787</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,19 +3277,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591743</v>
+        <v>128591105</v>
       </c>
       <c r="B25" t="n">
         <v>98591</v>
@@ -3317,20 +3317,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575392</v>
+        <v>575470</v>
       </c>
       <c r="R25" t="n">
-        <v>6373787</v>
+        <v>6373770</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,7 +3363,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3373,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,61 +3388,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591105</v>
+        <v>128591716</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>95905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575470</v>
+        <v>575425</v>
       </c>
       <c r="R26" t="n">
-        <v>6373770</v>
+        <v>6373803</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594506</v>
+        <v>128592340</v>
       </c>
       <c r="B41" t="n">
-        <v>79708</v>
+        <v>57686</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5086,37 +5086,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575410</v>
+        <v>575425</v>
       </c>
       <c r="R41" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594384</v>
+        <v>128594506</v>
       </c>
       <c r="B42" t="n">
         <v>79708</v>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575490</v>
+        <v>575410</v>
       </c>
       <c r="R42" t="n">
-        <v>6373927</v>
+        <v>6373926</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5289,10 +5294,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128592340</v>
+        <v>128594384</v>
       </c>
       <c r="B43" t="n">
-        <v>57686</v>
+        <v>79708</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,42 +5305,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575425</v>
+        <v>575490</v>
       </c>
       <c r="R43" t="n">
-        <v>6373803</v>
+        <v>6373927</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>79708</v>
+        <v>96187</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R48" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,45 +5973,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594164</v>
+        <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>56880</v>
+        <v>79708</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575441</v>
+        <v>575489</v>
       </c>
       <c r="R49" t="n">
-        <v>6373840</v>
+        <v>6373908</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6054,11 +6054,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6085,10 +6080,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594598</v>
+        <v>128594164</v>
       </c>
       <c r="B50" t="n">
-        <v>96187</v>
+        <v>56880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6096,34 +6091,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575422</v>
+        <v>575441</v>
       </c>
       <c r="R50" t="n">
-        <v>6373890</v>
+        <v>6373840</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6166,6 +6161,11 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128594457</v>
+        <v>128593162</v>
       </c>
       <c r="B57" t="n">
-        <v>92756</v>
+        <v>97462</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,41 +6882,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575490</v>
+        <v>575378</v>
       </c>
       <c r="R57" t="n">
-        <v>6373927</v>
+        <v>6373836</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6945,7 +6950,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6955,7 +6960,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6970,22 +6975,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>97462</v>
+        <v>92756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,46 +6998,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,12 +7086,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7224,42 +7224,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B60" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7268,10 +7264,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R60" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7303,7 +7299,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7309,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7340,38 +7336,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R61" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1825,48 +1825,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128590113</v>
+        <v>128592766</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>57683</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575564</v>
+        <v>575425</v>
       </c>
       <c r="R12" t="n">
-        <v>6373780</v>
+        <v>6373803</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,57 +1941,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592766</v>
+        <v>128590113</v>
       </c>
       <c r="B13" t="n">
-        <v>57683</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575425</v>
+        <v>575564</v>
       </c>
       <c r="R13" t="n">
-        <v>6373803</v>
+        <v>6373780</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,7 +2051,7 @@
         <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373844</v>
+        <v>6373845</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2167,7 +2167,7 @@
         <v>128594706</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96873</v>
+        <v>96874</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,53 +2499,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128591846</v>
+        <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>57686</v>
+        <v>96188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575382</v>
+        <v>575401</v>
       </c>
       <c r="R18" t="n">
-        <v>6373783</v>
+        <v>6373830</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2574,7 +2569,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2579,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,19 +2594,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128589508</v>
+        <v>128591846</v>
       </c>
       <c r="B19" t="n">
         <v>57686</v>
@@ -2639,11 +2634,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2651,17 +2642,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575483</v>
+        <v>575382</v>
       </c>
       <c r="R19" t="n">
-        <v>6373688</v>
+        <v>6373783</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2690,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,57 +2706,66 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128593153</v>
+        <v>128589508</v>
       </c>
       <c r="B20" t="n">
-        <v>96187</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575401</v>
+        <v>575483</v>
       </c>
       <c r="R20" t="n">
-        <v>6373830</v>
+        <v>6373688</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,57 +2834,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128593719</v>
+        <v>128591716</v>
       </c>
       <c r="B21" t="n">
-        <v>98591</v>
+        <v>95906</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575407</v>
+        <v>575425</v>
       </c>
       <c r="R21" t="n">
-        <v>6373854</v>
+        <v>6373803</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2913,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2929,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128594429</v>
+        <v>128593719</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2971,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2994,13 +2985,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575431</v>
+        <v>575407</v>
       </c>
       <c r="R22" t="n">
-        <v>6373926</v>
+        <v>6373854</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3029,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594789</v>
+        <v>128594429</v>
       </c>
       <c r="B23" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,27 +3087,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575404</v>
+        <v>575431</v>
       </c>
       <c r="R23" t="n">
-        <v>6373845</v>
+        <v>6373926</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3145,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,22 +3161,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128591743</v>
+        <v>128594789</v>
       </c>
       <c r="B24" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,20 +3201,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575392</v>
+        <v>575404</v>
       </c>
       <c r="R24" t="n">
-        <v>6373787</v>
+        <v>6373845</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,22 +3277,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591105</v>
+        <v>128591743</v>
       </c>
       <c r="B25" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,24 +3317,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575470</v>
+        <v>575392</v>
       </c>
       <c r="R25" t="n">
-        <v>6373770</v>
+        <v>6373787</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3373,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,57 +3384,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591716</v>
+        <v>128591105</v>
       </c>
       <c r="B26" t="n">
-        <v>95905</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575425</v>
+        <v>575470</v>
       </c>
       <c r="R26" t="n">
-        <v>6373803</v>
+        <v>6373770</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,57 +3507,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>57683</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R27" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3586,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3596,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3623,53 +3619,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>57683</v>
+        <v>98592</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R28" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3735,48 +3735,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B29" t="n">
-        <v>91486</v>
+        <v>98592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R29" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3805,7 +3814,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3815,7 +3824,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,69 +3839,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B30" t="n">
-        <v>98591</v>
+        <v>91487</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R30" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,12 +3946,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4073,7 +4073,7 @@
         <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,53 +4391,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B35" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R35" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4466,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4480,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,69 +4495,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R36" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6527,57 +6527,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128593763</v>
+        <v>128593706</v>
       </c>
       <c r="B54" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575376</v>
+        <v>575366</v>
       </c>
       <c r="R54" t="n">
-        <v>6373829</v>
+        <v>6373838</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6606,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6616,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6631,65 +6627,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128593706</v>
+        <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575366</v>
+        <v>575407</v>
       </c>
       <c r="R55" t="n">
-        <v>6373838</v>
+        <v>6373799</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6755,10 +6755,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128594919</v>
+        <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6788,24 +6788,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575407</v>
+        <v>575376</v>
       </c>
       <c r="R56" t="n">
-        <v>6373799</v>
+        <v>6373829</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,22 +6859,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>97462</v>
+        <v>92757</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,46 +6882,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R57" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6950,7 +6945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6955,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6975,22 +6970,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128594457</v>
+        <v>128593162</v>
       </c>
       <c r="B58" t="n">
-        <v>92756</v>
+        <v>97463</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6998,41 +6993,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575490</v>
+        <v>575378</v>
       </c>
       <c r="R58" t="n">
-        <v>6373927</v>
+        <v>6373836</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,12 +7086,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7224,38 +7224,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B60" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7264,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R60" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7299,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7336,42 +7340,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B61" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R61" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128533571</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128534193</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>128534411</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128548728</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>91514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,24 +1405,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R8" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B9" t="n">
-        <v>91487</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1521,19 +1516,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R9" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,7 +1602,7 @@
         <v>128548722</v>
       </c>
       <c r="B10" t="n">
-        <v>58366</v>
+        <v>58393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>128534744</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,57 +1825,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128592766</v>
+        <v>128590113</v>
       </c>
       <c r="B12" t="n">
-        <v>57683</v>
+        <v>79735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575425</v>
+        <v>575564</v>
       </c>
       <c r="R12" t="n">
-        <v>6373803</v>
+        <v>6373780</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,48 +1932,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128590113</v>
+        <v>128592766</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>57710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575564</v>
+        <v>575425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373780</v>
+        <v>6373803</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,7 +2051,7 @@
         <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373845</v>
+        <v>6373844</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2164,57 +2164,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>58393</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R15" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,65 +2264,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>58366</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R16" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96874</v>
+        <v>96901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128591846</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>128589508</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2834,48 +2834,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128591716</v>
+        <v>128593719</v>
       </c>
       <c r="B21" t="n">
-        <v>95906</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575407</v>
       </c>
       <c r="R21" t="n">
-        <v>6373803</v>
+        <v>6373854</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,22 +2938,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128593719</v>
+        <v>128594429</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2980,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2985,13 +2994,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575407</v>
+        <v>575431</v>
       </c>
       <c r="R22" t="n">
-        <v>6373854</v>
+        <v>6373926</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,10 +3066,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594429</v>
+        <v>128594789</v>
       </c>
       <c r="B23" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,27 +3096,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575431</v>
+        <v>575404</v>
       </c>
       <c r="R23" t="n">
-        <v>6373926</v>
+        <v>6373845</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3136,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,22 +3170,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128594789</v>
+        <v>128591743</v>
       </c>
       <c r="B24" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,29 +3210,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575404</v>
+        <v>575392</v>
       </c>
       <c r="R24" t="n">
-        <v>6373845</v>
+        <v>6373787</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,22 +3277,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591743</v>
+        <v>128591105</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,20 +3317,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575392</v>
+        <v>575470</v>
       </c>
       <c r="R25" t="n">
-        <v>6373787</v>
+        <v>6373770</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,7 +3363,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3373,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,61 +3388,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591105</v>
+        <v>128591716</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>95933</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575470</v>
+        <v>575425</v>
       </c>
       <c r="R26" t="n">
-        <v>6373770</v>
+        <v>6373803</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3510,7 +3510,7 @@
         <v>128593463</v>
       </c>
       <c r="B27" t="n">
-        <v>57683</v>
+        <v>57710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,57 +3735,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>91514</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R29" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3814,7 +3805,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3824,7 +3815,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,60 +3830,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>91487</v>
+        <v>98619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R30" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,62 +3946,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>98619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R31" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4033,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,45 +4065,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B32" t="n">
-        <v>98592</v>
+        <v>57713</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R32" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,57 +4391,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B35" t="n">
-        <v>98592</v>
+        <v>57713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R35" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4470,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,65 +4491,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B36" t="n">
-        <v>57686</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R36" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128594351</v>
+        <v>128591526</v>
       </c>
       <c r="B38" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,17 +4771,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575496</v>
+        <v>575421</v>
       </c>
       <c r="R38" t="n">
-        <v>6373918</v>
+        <v>6373766</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4847,10 +4847,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128591526</v>
+        <v>128594351</v>
       </c>
       <c r="B39" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,17 +4883,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575421</v>
+        <v>575496</v>
       </c>
       <c r="R39" t="n">
-        <v>6373766</v>
+        <v>6373918</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128592340</v>
+        <v>128594506</v>
       </c>
       <c r="B41" t="n">
-        <v>57686</v>
+        <v>79735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5086,42 +5086,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575425</v>
+        <v>575410</v>
       </c>
       <c r="R41" t="n">
-        <v>6373803</v>
+        <v>6373926</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5187,10 +5182,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594506</v>
+        <v>128594384</v>
       </c>
       <c r="B42" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575410</v>
+        <v>575490</v>
       </c>
       <c r="R42" t="n">
-        <v>6373926</v>
+        <v>6373927</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5294,10 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128594384</v>
+        <v>128592340</v>
       </c>
       <c r="B43" t="n">
-        <v>79708</v>
+        <v>57713</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,37 +5300,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575490</v>
+        <v>575425</v>
       </c>
       <c r="R43" t="n">
-        <v>6373927</v>
+        <v>6373803</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>128594164</v>
       </c>
       <c r="B50" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6192,45 +6192,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128593352</v>
+        <v>128594133</v>
       </c>
       <c r="B51" t="n">
-        <v>79708</v>
+        <v>105682</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575401</v>
+        <v>575441</v>
       </c>
       <c r="R51" t="n">
-        <v>6373862</v>
+        <v>6373840</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6299,54 +6308,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128594133</v>
+        <v>128593352</v>
       </c>
       <c r="B52" t="n">
-        <v>105654</v>
+        <v>79735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575441</v>
+        <v>575401</v>
       </c>
       <c r="R52" t="n">
-        <v>6373840</v>
+        <v>6373862</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128589055</v>
+        <v>128593706</v>
       </c>
       <c r="B53" t="n">
-        <v>58059</v>
+        <v>57713</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575467</v>
+        <v>575366</v>
       </c>
       <c r="R53" t="n">
-        <v>6373701</v>
+        <v>6373838</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,27 +6527,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B54" t="n">
-        <v>57686</v>
+        <v>58086</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6558,22 +6558,22 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R54" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6642,7 +6642,7 @@
         <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>128593162</v>
       </c>
       <c r="B58" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>128601004</v>
       </c>
       <c r="B59" t="n">
-        <v>43952</v>
+        <v>43979</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7224,42 +7224,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B60" t="n">
-        <v>98592</v>
+        <v>57713</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7268,10 +7264,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R60" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7303,7 +7299,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7309,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7340,38 +7336,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>57686</v>
+        <v>98619</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R61" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>128740640</v>
       </c>
       <c r="B63" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>128739848</v>
       </c>
       <c r="B64" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -3507,53 +3507,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B27" t="n">
-        <v>57710</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R27" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3596,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,57 +3623,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B28" t="n">
-        <v>98619</v>
+        <v>57710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R28" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4391,53 +4391,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B35" t="n">
-        <v>57713</v>
+        <v>98619</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R35" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4466,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4480,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,69 +4495,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>57713</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R36" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6192,54 +6192,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128594133</v>
+        <v>128593352</v>
       </c>
       <c r="B51" t="n">
-        <v>105682</v>
+        <v>79735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575441</v>
+        <v>575401</v>
       </c>
       <c r="R51" t="n">
-        <v>6373840</v>
+        <v>6373862</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6308,45 +6299,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128593352</v>
+        <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>79735</v>
+        <v>105682</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575401</v>
+        <v>575441</v>
       </c>
       <c r="R52" t="n">
-        <v>6373862</v>
+        <v>6373840</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B53" t="n">
-        <v>57713</v>
+        <v>58086</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R53" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,27 +6527,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128589055</v>
+        <v>128593706</v>
       </c>
       <c r="B54" t="n">
-        <v>58086</v>
+        <v>57713</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6558,22 +6558,22 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575467</v>
+        <v>575366</v>
       </c>
       <c r="R54" t="n">
-        <v>6373701</v>
+        <v>6373838</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B57" t="n">
-        <v>92784</v>
+        <v>43979</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,41 +6882,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6945,7 +6954,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6955,7 +6964,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6964,6 +6978,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6982,10 +6997,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>97490</v>
+        <v>92784</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,46 +7008,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,22 +7096,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B59" t="n">
-        <v>43979</v>
+        <v>97490</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7109,50 +7119,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R59" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7205,19 +7206,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B8" t="n">
-        <v>91514</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,19 +1405,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R8" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>91519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,24 +1521,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R9" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,7 +1721,7 @@
         <v>128534744</v>
       </c>
       <c r="B11" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128590113</v>
       </c>
       <c r="B12" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373844</v>
+        <v>6373845</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2279,7 +2279,7 @@
         <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96901</v>
+        <v>96907</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>128593719</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>128594429</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>128594789</v>
       </c>
       <c r="B23" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>128591743</v>
       </c>
       <c r="B24" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128591105</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>128591716</v>
       </c>
       <c r="B26" t="n">
-        <v>95933</v>
+        <v>95939</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3507,57 +3507,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>57710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R27" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3586,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3596,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3623,53 +3619,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>57710</v>
+        <v>98625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R28" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,7 +3738,7 @@
         <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3958,45 +3958,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B31" t="n">
-        <v>98619</v>
+        <v>57713</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R31" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,50 +4070,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>57713</v>
+        <v>98625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R32" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>128594570</v>
       </c>
       <c r="B35" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128591526</v>
+        <v>128594351</v>
       </c>
       <c r="B38" t="n">
         <v>57713</v>
@@ -4771,17 +4771,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575421</v>
+        <v>575496</v>
       </c>
       <c r="R38" t="n">
-        <v>6373766</v>
+        <v>6373918</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4847,7 +4847,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128594351</v>
+        <v>128591526</v>
       </c>
       <c r="B39" t="n">
         <v>57713</v>
@@ -4883,17 +4883,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575496</v>
+        <v>575421</v>
       </c>
       <c r="R39" t="n">
-        <v>6373918</v>
+        <v>6373766</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594506</v>
+        <v>128594384</v>
       </c>
       <c r="B41" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575410</v>
+        <v>575490</v>
       </c>
       <c r="R41" t="n">
-        <v>6373926</v>
+        <v>6373927</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594384</v>
+        <v>128594506</v>
       </c>
       <c r="B42" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575490</v>
+        <v>575410</v>
       </c>
       <c r="R42" t="n">
-        <v>6373927</v>
+        <v>6373926</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594598</v>
+        <v>128594199</v>
       </c>
       <c r="B48" t="n">
-        <v>96215</v>
+        <v>79739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575422</v>
+        <v>575489</v>
       </c>
       <c r="R48" t="n">
-        <v>6373890</v>
+        <v>6373908</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,32 +5973,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B49" t="n">
-        <v>79735</v>
+        <v>96221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R49" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6195,7 +6195,7 @@
         <v>128593352</v>
       </c>
       <c r="B51" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B57" t="n">
-        <v>43979</v>
+        <v>97496</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,50 +6882,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R57" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6954,7 +6950,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6964,12 +6960,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,29 +6969,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B58" t="n">
-        <v>92784</v>
+        <v>43979</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7008,41 +6998,50 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7071,7 +7070,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7080,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7090,6 +7094,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7108,10 +7113,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B59" t="n">
-        <v>97490</v>
+        <v>92789</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7119,46 +7124,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R59" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7212,12 +7212,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7339,7 +7339,7 @@
         <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>91524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,24 +1405,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R8" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B9" t="n">
-        <v>91519</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1521,19 +1516,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R9" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2051,7 +2051,7 @@
         <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373845</v>
+        <v>6373844</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2164,53 +2164,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B15" t="n">
-        <v>58393</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R15" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,69 +2268,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>58393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R16" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96907</v>
+        <v>96914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128591846</v>
+        <v>128589508</v>
       </c>
       <c r="B19" t="n">
         <v>57713</v>
@@ -2634,7 +2634,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2642,17 +2646,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575382</v>
+        <v>575483</v>
       </c>
       <c r="R19" t="n">
-        <v>6373783</v>
+        <v>6373688</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2695,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,19 +2710,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128589508</v>
+        <v>128591846</v>
       </c>
       <c r="B20" t="n">
         <v>57713</v>
@@ -2746,11 +2750,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2758,17 +2758,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575483</v>
+        <v>575382</v>
       </c>
       <c r="R20" t="n">
-        <v>6373688</v>
+        <v>6373783</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,69 +2822,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128593719</v>
+        <v>128591716</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>95946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575407</v>
+        <v>575425</v>
       </c>
       <c r="R21" t="n">
-        <v>6373854</v>
+        <v>6373803</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2913,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2929,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128594429</v>
+        <v>128593719</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2971,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2994,13 +2985,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575431</v>
+        <v>575407</v>
       </c>
       <c r="R22" t="n">
-        <v>6373926</v>
+        <v>6373854</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3029,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594789</v>
+        <v>128594429</v>
       </c>
       <c r="B23" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,27 +3087,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575404</v>
+        <v>575431</v>
       </c>
       <c r="R23" t="n">
-        <v>6373845</v>
+        <v>6373926</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3145,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,22 +3161,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128591743</v>
+        <v>128594789</v>
       </c>
       <c r="B24" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,20 +3201,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575392</v>
+        <v>575404</v>
       </c>
       <c r="R24" t="n">
-        <v>6373787</v>
+        <v>6373845</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,22 +3277,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591105</v>
+        <v>128591743</v>
       </c>
       <c r="B25" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,24 +3317,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575470</v>
+        <v>575392</v>
       </c>
       <c r="R25" t="n">
-        <v>6373770</v>
+        <v>6373787</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3373,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,57 +3384,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591716</v>
+        <v>128591105</v>
       </c>
       <c r="B26" t="n">
-        <v>95939</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575425</v>
+        <v>575470</v>
       </c>
       <c r="R26" t="n">
-        <v>6373803</v>
+        <v>6373770</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3622,7 +3622,7 @@
         <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,48 +3735,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B29" t="n">
-        <v>91519</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R29" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3805,7 +3814,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3815,7 +3824,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,69 +3839,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B30" t="n">
-        <v>98625</v>
+        <v>91524</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R30" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,12 +3946,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4073,7 +4073,7 @@
         <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,57 +4391,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B35" t="n">
-        <v>98625</v>
+        <v>57713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R35" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4470,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,65 +4491,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B36" t="n">
-        <v>57713</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R36" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594384</v>
+        <v>128594506</v>
       </c>
       <c r="B41" t="n">
         <v>79739</v>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575490</v>
+        <v>575410</v>
       </c>
       <c r="R41" t="n">
-        <v>6373927</v>
+        <v>6373926</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594506</v>
+        <v>128594384</v>
       </c>
       <c r="B42" t="n">
         <v>79739</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575410</v>
+        <v>575490</v>
       </c>
       <c r="R42" t="n">
-        <v>6373926</v>
+        <v>6373927</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594598</v>
+        <v>128594164</v>
       </c>
       <c r="B49" t="n">
-        <v>96221</v>
+        <v>56907</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,34 +5984,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575422</v>
+        <v>575441</v>
       </c>
       <c r="R49" t="n">
-        <v>6373890</v>
+        <v>6373840</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6054,6 +6054,11 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6080,10 +6085,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594164</v>
+        <v>128594598</v>
       </c>
       <c r="B50" t="n">
-        <v>56907</v>
+        <v>96228</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6091,34 +6096,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575441</v>
+        <v>575422</v>
       </c>
       <c r="R50" t="n">
-        <v>6373840</v>
+        <v>6373890</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6161,11 +6166,6 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128589055</v>
+        <v>128593706</v>
       </c>
       <c r="B53" t="n">
-        <v>58086</v>
+        <v>57713</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575467</v>
+        <v>575366</v>
       </c>
       <c r="R53" t="n">
-        <v>6373701</v>
+        <v>6373838</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,27 +6527,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B54" t="n">
-        <v>57713</v>
+        <v>58086</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6558,22 +6558,22 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R54" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6642,7 +6642,7 @@
         <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128593162</v>
+        <v>128601004</v>
       </c>
       <c r="B57" t="n">
-        <v>97496</v>
+        <v>43979</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,46 +6882,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>101735</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>6373836</v>
+        <v>6373840</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6950,7 +6954,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6964,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6969,28 +6978,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128601004</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>43979</v>
+        <v>92794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6998,50 +7008,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101735</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373840</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7070,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7080,12 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7094,7 +7090,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7113,10 +7108,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128594457</v>
+        <v>128593162</v>
       </c>
       <c r="B59" t="n">
-        <v>92789</v>
+        <v>97503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7124,41 +7119,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575490</v>
+        <v>575378</v>
       </c>
       <c r="R59" t="n">
-        <v>6373927</v>
+        <v>6373836</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7212,12 +7212,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7339,7 +7339,7 @@
         <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8485,6 +8485,126 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128740331</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>575546</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6373449</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1825,48 +1825,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128590113</v>
+        <v>128593782</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575564</v>
+        <v>575415</v>
       </c>
       <c r="R12" t="n">
-        <v>6373780</v>
+        <v>6373845</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,12 +1929,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2048,57 +2057,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128593782</v>
+        <v>128590113</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>79739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575415</v>
+        <v>575564</v>
       </c>
       <c r="R14" t="n">
-        <v>6373844</v>
+        <v>6373780</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,12 +2152,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128589508</v>
+        <v>128591846</v>
       </c>
       <c r="B19" t="n">
         <v>57713</v>
@@ -2634,11 +2634,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2646,17 +2642,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575483</v>
+        <v>575382</v>
       </c>
       <c r="R19" t="n">
-        <v>6373688</v>
+        <v>6373783</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2685,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,19 +2706,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128591846</v>
+        <v>128589508</v>
       </c>
       <c r="B20" t="n">
         <v>57713</v>
@@ -2750,7 +2746,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2758,17 +2758,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575382</v>
+        <v>575483</v>
       </c>
       <c r="R20" t="n">
-        <v>6373783</v>
+        <v>6373688</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,12 +2822,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128593719</v>
+        <v>128591105</v>
       </c>
       <c r="B22" t="n">
         <v>98632</v>
@@ -2971,27 +2971,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575407</v>
+        <v>575470</v>
       </c>
       <c r="R22" t="n">
-        <v>6373854</v>
+        <v>6373770</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,19 +3040,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594429</v>
+        <v>128593719</v>
       </c>
       <c r="B23" t="n">
         <v>98632</v>
@@ -3087,7 +3082,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3101,13 +3096,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575431</v>
+        <v>575407</v>
       </c>
       <c r="R23" t="n">
-        <v>6373926</v>
+        <v>6373854</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3136,7 +3131,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3141,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,7 +3168,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128594789</v>
+        <v>128591743</v>
       </c>
       <c r="B24" t="n">
         <v>98632</v>
@@ -3201,29 +3196,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575404</v>
+        <v>575392</v>
       </c>
       <c r="R24" t="n">
-        <v>6373845</v>
+        <v>6373787</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,19 +3263,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591743</v>
+        <v>128594789</v>
       </c>
       <c r="B25" t="n">
         <v>98632</v>
@@ -3317,20 +3303,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575392</v>
+        <v>575404</v>
       </c>
       <c r="R25" t="n">
-        <v>6373787</v>
+        <v>6373845</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3364,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,19 +3379,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591105</v>
+        <v>128594429</v>
       </c>
       <c r="B26" t="n">
         <v>98632</v>
@@ -3426,22 +3421,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575470</v>
+        <v>575431</v>
       </c>
       <c r="R26" t="n">
-        <v>6373770</v>
+        <v>6373926</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,12 +3495,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3735,57 +3735,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>91524</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R29" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3814,7 +3805,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3824,7 +3815,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,60 +3830,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>91524</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R30" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,12 +3946,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4391,53 +4391,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B35" t="n">
-        <v>57713</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R35" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4466,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4480,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,69 +4495,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>57713</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R36" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5075,48 +5075,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594506</v>
+        <v>128594618</v>
       </c>
       <c r="B41" t="n">
-        <v>79739</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575410</v>
+        <v>575433</v>
       </c>
       <c r="R41" t="n">
-        <v>6373926</v>
+        <v>6373862</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,60 +5170,69 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594384</v>
+        <v>128593762</v>
       </c>
       <c r="B42" t="n">
-        <v>79739</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575490</v>
+        <v>575411</v>
       </c>
       <c r="R42" t="n">
-        <v>6373927</v>
+        <v>6373848</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5252,7 +5261,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5271,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5277,22 +5286,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128592340</v>
+        <v>128594506</v>
       </c>
       <c r="B43" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,42 +5309,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575425</v>
+        <v>575410</v>
       </c>
       <c r="R43" t="n">
-        <v>6373803</v>
+        <v>6373926</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5401,48 +5405,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128594618</v>
+        <v>128594384</v>
       </c>
       <c r="B44" t="n">
-        <v>98632</v>
+        <v>79739</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575433</v>
+        <v>575490</v>
       </c>
       <c r="R44" t="n">
-        <v>6373862</v>
+        <v>6373927</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5471,7 +5475,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5481,7 +5485,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,69 +5500,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128593762</v>
+        <v>128592340</v>
       </c>
       <c r="B45" t="n">
-        <v>98632</v>
+        <v>57713</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575411</v>
+        <v>575425</v>
       </c>
       <c r="R45" t="n">
-        <v>6373848</v>
+        <v>6373803</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>79739</v>
+        <v>96228</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R48" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,45 +5973,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594164</v>
+        <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>56907</v>
+        <v>79739</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575441</v>
+        <v>575489</v>
       </c>
       <c r="R49" t="n">
-        <v>6373840</v>
+        <v>6373908</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6054,11 +6054,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6085,10 +6080,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594598</v>
+        <v>128594164</v>
       </c>
       <c r="B50" t="n">
-        <v>96228</v>
+        <v>56907</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6096,34 +6091,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575422</v>
+        <v>575441</v>
       </c>
       <c r="R50" t="n">
-        <v>6373890</v>
+        <v>6373840</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6166,6 +6161,11 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B53" t="n">
-        <v>57713</v>
+        <v>58086</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R53" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,38 +6527,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128589055</v>
+        <v>128594919</v>
       </c>
       <c r="B54" t="n">
-        <v>58086</v>
+        <v>98632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6567,13 +6571,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575467</v>
+        <v>575407</v>
       </c>
       <c r="R54" t="n">
-        <v>6373701</v>
+        <v>6373799</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6606,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6616,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6639,7 +6643,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128594919</v>
+        <v>128593763</v>
       </c>
       <c r="B55" t="n">
         <v>98632</v>
@@ -6672,24 +6676,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575407</v>
+        <v>575376</v>
       </c>
       <c r="R55" t="n">
-        <v>6373799</v>
+        <v>6373829</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,7 +6722,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6728,7 +6732,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6743,69 +6747,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128593763</v>
+        <v>128593706</v>
       </c>
       <c r="B56" t="n">
-        <v>98632</v>
+        <v>57713</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575376</v>
+        <v>575366</v>
       </c>
       <c r="R56" t="n">
-        <v>6373829</v>
+        <v>6373838</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,22 +6859,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128601004</v>
+        <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>43979</v>
+        <v>92794</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,50 +6882,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101735</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575490</v>
       </c>
       <c r="R57" t="n">
-        <v>6373840</v>
+        <v>6373927</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6954,7 +6945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6964,12 +6955,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,7 +6964,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6997,10 +6982,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128594457</v>
+        <v>128593162</v>
       </c>
       <c r="B58" t="n">
-        <v>92794</v>
+        <v>97503</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7008,41 +6993,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575490</v>
+        <v>575378</v>
       </c>
       <c r="R58" t="n">
-        <v>6373927</v>
+        <v>6373836</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7071,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,22 +7086,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128593162</v>
+        <v>128601004</v>
       </c>
       <c r="B59" t="n">
-        <v>97503</v>
+        <v>43979</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7119,46 +7109,50 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>101735</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R59" t="n">
-        <v>6373836</v>
+        <v>6373840</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7191,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7206,18 +7205,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -2164,57 +2164,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>58393</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R15" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,65 +2264,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>58393</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R16" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -5075,48 +5075,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594618</v>
+        <v>128594506</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>79739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575433</v>
+        <v>575410</v>
       </c>
       <c r="R41" t="n">
-        <v>6373862</v>
+        <v>6373926</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,69 +5170,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128593762</v>
+        <v>128594384</v>
       </c>
       <c r="B42" t="n">
-        <v>98632</v>
+        <v>79739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575411</v>
+        <v>575490</v>
       </c>
       <c r="R42" t="n">
-        <v>6373848</v>
+        <v>6373927</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5261,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5271,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5286,22 +5277,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128594506</v>
+        <v>128592340</v>
       </c>
       <c r="B43" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5309,37 +5300,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575410</v>
+        <v>575425</v>
       </c>
       <c r="R43" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5405,48 +5401,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128594384</v>
+        <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>79739</v>
+        <v>98632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575490</v>
+        <v>575433</v>
       </c>
       <c r="R44" t="n">
-        <v>6373927</v>
+        <v>6373862</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5475,7 +5471,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5485,7 +5481,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5500,65 +5496,69 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128592340</v>
+        <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>57713</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575425</v>
+        <v>575411</v>
       </c>
       <c r="R45" t="n">
-        <v>6373803</v>
+        <v>6373848</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,69 +5612,73 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128593944</v>
+        <v>128600928</v>
       </c>
       <c r="B46" t="n">
-        <v>98632</v>
+        <v>5362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>101728</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575453</v>
+        <v>575524</v>
       </c>
       <c r="R46" t="n">
-        <v>6373840</v>
+        <v>6373718</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5703,7 +5707,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5713,7 +5717,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fanns på en liggande grov asplåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,79 +5731,76 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128600928</v>
+        <v>128593944</v>
       </c>
       <c r="B47" t="n">
-        <v>5362</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575524</v>
+        <v>575453</v>
       </c>
       <c r="R47" t="n">
-        <v>6373718</v>
+        <v>6373840</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5823,7 +5829,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5833,12 +5839,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fanns på en liggande grov asplåga</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,51 +5848,50 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594598</v>
+        <v>128594199</v>
       </c>
       <c r="B48" t="n">
-        <v>96228</v>
+        <v>79739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575422</v>
+        <v>575489</v>
       </c>
       <c r="R48" t="n">
-        <v>6373890</v>
+        <v>6373908</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,32 +5973,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B49" t="n">
-        <v>79739</v>
+        <v>96228</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R49" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6527,57 +6527,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128594919</v>
+        <v>128593706</v>
       </c>
       <c r="B54" t="n">
-        <v>98632</v>
+        <v>57713</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575407</v>
+        <v>575366</v>
       </c>
       <c r="R54" t="n">
-        <v>6373799</v>
+        <v>6373838</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6606,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6616,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6643,7 +6639,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128593763</v>
+        <v>128594919</v>
       </c>
       <c r="B55" t="n">
         <v>98632</v>
@@ -6676,24 +6672,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575376</v>
+        <v>575407</v>
       </c>
       <c r="R55" t="n">
-        <v>6373829</v>
+        <v>6373799</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6722,7 +6718,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6732,7 +6728,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6747,65 +6743,69 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128593706</v>
+        <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>57713</v>
+        <v>98632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575366</v>
+        <v>575376</v>
       </c>
       <c r="R56" t="n">
-        <v>6373838</v>
+        <v>6373829</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,22 +6859,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B57" t="n">
-        <v>92794</v>
+        <v>43979</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,41 +6882,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6945,7 +6954,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6955,7 +6964,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6964,6 +6978,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6982,10 +6997,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>97503</v>
+        <v>92794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,46 +7008,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,22 +7096,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B59" t="n">
-        <v>43979</v>
+        <v>97503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7109,50 +7119,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R59" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7205,19 +7206,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128533571</v>
       </c>
       <c r="B3" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128534193</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>128534411</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128548728</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B8" t="n">
-        <v>91524</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,19 +1405,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R8" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>91528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,24 +1521,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R9" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,7 +1602,7 @@
         <v>128548722</v>
       </c>
       <c r="B10" t="n">
-        <v>58393</v>
+        <v>58397</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>128534744</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,57 +1825,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128593782</v>
+        <v>128592766</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>57714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575415</v>
+        <v>575425</v>
       </c>
       <c r="R12" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,69 +1929,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592766</v>
+        <v>128593782</v>
       </c>
       <c r="B13" t="n">
-        <v>57710</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575425</v>
+        <v>575415</v>
       </c>
       <c r="R13" t="n">
-        <v>6373803</v>
+        <v>6373845</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,12 +2045,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
         <v>128590113</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>128593286</v>
       </c>
       <c r="B15" t="n">
-        <v>58393</v>
+        <v>58397</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128591846</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>128589508</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2834,48 +2834,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128591716</v>
+        <v>128593719</v>
       </c>
       <c r="B21" t="n">
-        <v>95946</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575407</v>
       </c>
       <c r="R21" t="n">
-        <v>6373803</v>
+        <v>6373854</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,22 +2938,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128591105</v>
+        <v>128594429</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,22 +2980,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575470</v>
+        <v>575431</v>
       </c>
       <c r="R22" t="n">
-        <v>6373770</v>
+        <v>6373926</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3015,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,22 +3054,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128593719</v>
+        <v>128594789</v>
       </c>
       <c r="B23" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,24 +3099,24 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575407</v>
+        <v>575404</v>
       </c>
       <c r="R23" t="n">
-        <v>6373854</v>
+        <v>6373845</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,12 +3170,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3171,7 +3185,7 @@
         <v>128591743</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,10 +3289,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128594789</v>
+        <v>128591105</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,12 +3319,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3319,13 +3328,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575404</v>
+        <v>575470</v>
       </c>
       <c r="R25" t="n">
-        <v>6373845</v>
+        <v>6373770</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3391,57 +3400,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128594429</v>
+        <v>128591716</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>95950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575431</v>
+        <v>575425</v>
       </c>
       <c r="R26" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,12 +3495,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3510,7 +3510,7 @@
         <v>128593463</v>
       </c>
       <c r="B27" t="n">
-        <v>57710</v>
+        <v>57714</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128594827</v>
       </c>
       <c r="B31" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,57 +4391,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>57717</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R35" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4470,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,65 +4491,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B36" t="n">
-        <v>57713</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R36" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>128594351</v>
       </c>
       <c r="B38" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>128591526</v>
       </c>
       <c r="B39" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>128594506</v>
       </c>
       <c r="B41" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>128594384</v>
       </c>
       <c r="B42" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>128592340</v>
       </c>
       <c r="B43" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,61 +5624,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128600928</v>
+        <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>5362</v>
+        <v>98636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575524</v>
+        <v>575453</v>
       </c>
       <c r="R46" t="n">
-        <v>6373718</v>
+        <v>6373840</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5707,7 +5703,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5717,12 +5713,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Fanns på en liggande grov asplåga</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5731,76 +5722,79 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128593944</v>
+        <v>128600928</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>5362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>101728</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575453</v>
+        <v>575524</v>
       </c>
       <c r="R47" t="n">
-        <v>6373840</v>
+        <v>6373718</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5829,7 +5823,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5839,7 +5833,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fanns på en liggande grov asplåga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5848,50 +5847,51 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>79739</v>
+        <v>96232</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R48" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,32 +5973,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594598</v>
+        <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>96228</v>
+        <v>79743</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575422</v>
+        <v>575489</v>
       </c>
       <c r="R49" t="n">
-        <v>6373890</v>
+        <v>6373908</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6083,7 +6083,7 @@
         <v>128594164</v>
       </c>
       <c r="B50" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>128593352</v>
       </c>
       <c r="B51" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128589055</v>
+        <v>128593706</v>
       </c>
       <c r="B53" t="n">
-        <v>58086</v>
+        <v>57717</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575467</v>
+        <v>575366</v>
       </c>
       <c r="R53" t="n">
-        <v>6373701</v>
+        <v>6373838</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,27 +6527,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B54" t="n">
-        <v>57713</v>
+        <v>58090</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6558,22 +6558,22 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R54" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6642,7 +6642,7 @@
         <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B57" t="n">
-        <v>43979</v>
+        <v>97507</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,50 +6882,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R57" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6954,7 +6950,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6964,12 +6960,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,29 +6969,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B58" t="n">
-        <v>92794</v>
+        <v>43980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7008,41 +6998,50 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7071,7 +7070,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7080,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7090,6 +7094,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7108,10 +7113,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B59" t="n">
-        <v>97503</v>
+        <v>92798</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7119,46 +7124,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R59" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7212,50 +7212,54 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B60" t="n">
-        <v>57713</v>
+        <v>98636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7264,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R60" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7299,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7336,42 +7340,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B61" t="n">
-        <v>98632</v>
+        <v>57717</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R61" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>128740640</v>
       </c>
       <c r="B63" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>128739848</v>
       </c>
       <c r="B64" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>91528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,24 +1405,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R8" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B9" t="n">
-        <v>91528</v>
+        <v>57717</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1521,19 +1516,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R9" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1825,57 +1825,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128592766</v>
+        <v>128590113</v>
       </c>
       <c r="B12" t="n">
-        <v>57714</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575425</v>
+        <v>575564</v>
       </c>
       <c r="R12" t="n">
-        <v>6373803</v>
+        <v>6373780</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2057,48 +2048,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128590113</v>
+        <v>128592766</v>
       </c>
       <c r="B14" t="n">
-        <v>79743</v>
+        <v>57714</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575564</v>
+        <v>575425</v>
       </c>
       <c r="R14" t="n">
-        <v>6373780</v>
+        <v>6373803</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3066,57 +3066,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594789</v>
+        <v>128591716</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>95950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575404</v>
+        <v>575425</v>
       </c>
       <c r="R23" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3182,7 +3173,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128591743</v>
+        <v>128594789</v>
       </c>
       <c r="B24" t="n">
         <v>98636</v>
@@ -3210,20 +3201,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575392</v>
+        <v>575404</v>
       </c>
       <c r="R24" t="n">
-        <v>6373787</v>
+        <v>6373845</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,19 +3277,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591105</v>
+        <v>128591743</v>
       </c>
       <c r="B25" t="n">
         <v>98636</v>
@@ -3317,24 +3317,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575470</v>
+        <v>575392</v>
       </c>
       <c r="R25" t="n">
-        <v>6373770</v>
+        <v>6373787</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3373,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,57 +3384,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591716</v>
+        <v>128591105</v>
       </c>
       <c r="B26" t="n">
-        <v>95950</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575425</v>
+        <v>575470</v>
       </c>
       <c r="R26" t="n">
-        <v>6373803</v>
+        <v>6373770</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3735,48 +3735,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B29" t="n">
-        <v>91528</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R29" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3805,7 +3814,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3815,7 +3824,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,69 +3839,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>91528</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R30" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,62 +3946,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B31" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R31" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4033,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,45 +4065,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B32" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R32" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5075,10 +5075,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594506</v>
+        <v>128592340</v>
       </c>
       <c r="B41" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5086,37 +5086,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575410</v>
+        <v>575425</v>
       </c>
       <c r="R41" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594384</v>
+        <v>128594506</v>
       </c>
       <c r="B42" t="n">
         <v>79743</v>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575490</v>
+        <v>575410</v>
       </c>
       <c r="R42" t="n">
-        <v>6373927</v>
+        <v>6373926</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5289,10 +5294,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128592340</v>
+        <v>128594384</v>
       </c>
       <c r="B43" t="n">
-        <v>57717</v>
+        <v>79743</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,42 +5305,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575425</v>
+        <v>575490</v>
       </c>
       <c r="R43" t="n">
-        <v>6373803</v>
+        <v>6373927</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128601004</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>43980</v>
+        <v>92798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6998,50 +6998,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101735</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373840</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7070,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7080,12 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7094,7 +7080,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7113,10 +7098,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B59" t="n">
-        <v>92798</v>
+        <v>43980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7124,41 +7109,50 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R59" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7191,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7206,6 +7205,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7224,42 +7224,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B60" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7268,10 +7264,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R60" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7303,7 +7299,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7309,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7340,38 +7336,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R61" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B8" t="n">
-        <v>91528</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,19 +1405,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R8" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>57717</v>
+        <v>91528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,24 +1521,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R9" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1932,57 +1932,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128593782</v>
+        <v>128592766</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>57714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575415</v>
+        <v>575425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,69 +2036,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592766</v>
+        <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>57714</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575425</v>
+        <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373803</v>
+        <v>6373845</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,12 +2152,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2499,48 +2499,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128593153</v>
+        <v>128591846</v>
       </c>
       <c r="B18" t="n">
-        <v>96232</v>
+        <v>57717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575401</v>
+        <v>575382</v>
       </c>
       <c r="R18" t="n">
-        <v>6373830</v>
+        <v>6373783</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2569,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2579,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,19 +2599,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128591846</v>
+        <v>128589508</v>
       </c>
       <c r="B19" t="n">
         <v>57717</v>
@@ -2634,7 +2639,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2642,17 +2651,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575382</v>
+        <v>575483</v>
       </c>
       <c r="R19" t="n">
-        <v>6373783</v>
+        <v>6373688</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,66 +2715,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128589508</v>
+        <v>128593153</v>
       </c>
       <c r="B20" t="n">
-        <v>57717</v>
+        <v>96232</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575483</v>
+        <v>575401</v>
       </c>
       <c r="R20" t="n">
-        <v>6373688</v>
+        <v>6373830</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,7 +2834,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128593719</v>
+        <v>128594789</v>
       </c>
       <c r="B21" t="n">
         <v>98636</v>
@@ -2867,24 +2867,24 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575407</v>
+        <v>575404</v>
       </c>
       <c r="R21" t="n">
-        <v>6373854</v>
+        <v>6373845</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,69 +2938,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128594429</v>
+        <v>128591716</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>95950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575431</v>
+        <v>575425</v>
       </c>
       <c r="R22" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3029,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,60 +3045,69 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128591716</v>
+        <v>128593719</v>
       </c>
       <c r="B23" t="n">
-        <v>95950</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575425</v>
+        <v>575407</v>
       </c>
       <c r="R23" t="n">
-        <v>6373803</v>
+        <v>6373854</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,19 +3161,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128594789</v>
+        <v>128594429</v>
       </c>
       <c r="B24" t="n">
         <v>98636</v>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575404</v>
+        <v>575431</v>
       </c>
       <c r="R24" t="n">
-        <v>6373845</v>
+        <v>6373926</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,12 +3277,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3507,53 +3507,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B27" t="n">
-        <v>57714</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R27" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3596,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,57 +3623,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>57714</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R28" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3735,57 +3735,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>91528</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R29" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3814,7 +3805,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3824,7 +3815,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,60 +3830,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>91528</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R30" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,12 +3946,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -5075,53 +5075,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128592340</v>
+        <v>128594618</v>
       </c>
       <c r="B41" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575425</v>
+        <v>575433</v>
       </c>
       <c r="R41" t="n">
-        <v>6373803</v>
+        <v>6373862</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5150,7 +5145,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5160,7 +5155,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,60 +5170,69 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594506</v>
+        <v>128593762</v>
       </c>
       <c r="B42" t="n">
-        <v>79743</v>
+        <v>98636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575410</v>
+        <v>575411</v>
       </c>
       <c r="R42" t="n">
-        <v>6373926</v>
+        <v>6373848</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5257,7 +5261,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5267,7 +5271,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5282,22 +5286,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128594384</v>
+        <v>128592340</v>
       </c>
       <c r="B43" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,37 +5309,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575490</v>
+        <v>575425</v>
       </c>
       <c r="R43" t="n">
-        <v>6373927</v>
+        <v>6373803</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5401,48 +5410,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128594618</v>
+        <v>128594506</v>
       </c>
       <c r="B44" t="n">
-        <v>98636</v>
+        <v>79743</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575433</v>
+        <v>575410</v>
       </c>
       <c r="R44" t="n">
-        <v>6373862</v>
+        <v>6373926</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5471,7 +5480,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5481,7 +5490,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,69 +5505,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128593762</v>
+        <v>128594384</v>
       </c>
       <c r="B45" t="n">
-        <v>98636</v>
+        <v>79743</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575411</v>
+        <v>575490</v>
       </c>
       <c r="R45" t="n">
-        <v>6373848</v>
+        <v>6373927</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594598</v>
+        <v>128594199</v>
       </c>
       <c r="B48" t="n">
-        <v>96232</v>
+        <v>79743</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575422</v>
+        <v>575489</v>
       </c>
       <c r="R48" t="n">
-        <v>6373890</v>
+        <v>6373908</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,32 +5973,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B49" t="n">
-        <v>79743</v>
+        <v>96232</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R49" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6192,45 +6192,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128593352</v>
+        <v>128594133</v>
       </c>
       <c r="B51" t="n">
-        <v>79743</v>
+        <v>105699</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575401</v>
+        <v>575441</v>
       </c>
       <c r="R51" t="n">
-        <v>6373862</v>
+        <v>6373840</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6299,54 +6308,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128594133</v>
+        <v>128593352</v>
       </c>
       <c r="B52" t="n">
-        <v>105699</v>
+        <v>79743</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575441</v>
+        <v>575401</v>
       </c>
       <c r="R52" t="n">
-        <v>6373840</v>
+        <v>6373862</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B53" t="n">
-        <v>57717</v>
+        <v>58090</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R53" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,53 +6527,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128589055</v>
+        <v>128593763</v>
       </c>
       <c r="B54" t="n">
-        <v>58090</v>
+        <v>98636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575467</v>
+        <v>575376</v>
       </c>
       <c r="R54" t="n">
-        <v>6373701</v>
+        <v>6373829</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6606,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6616,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6627,12 +6631,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6755,57 +6759,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128593763</v>
+        <v>128593706</v>
       </c>
       <c r="B56" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575376</v>
+        <v>575366</v>
       </c>
       <c r="R56" t="n">
-        <v>6373829</v>
+        <v>6373838</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,22 +6859,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>97507</v>
+        <v>92798</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,46 +6882,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R57" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6950,7 +6945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6955,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6975,22 +6970,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128594457</v>
+        <v>128593162</v>
       </c>
       <c r="B58" t="n">
-        <v>92798</v>
+        <v>97507</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6998,41 +6993,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575490</v>
+        <v>575378</v>
       </c>
       <c r="R58" t="n">
-        <v>6373927</v>
+        <v>6373836</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,12 +7086,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128533571</v>
       </c>
       <c r="B3" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128534193</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>128534411</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128548728</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128533348</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128548722</v>
       </c>
       <c r="B10" t="n">
-        <v>58397</v>
+        <v>58400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>128534744</v>
       </c>
       <c r="B11" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,48 +1825,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128590113</v>
+        <v>128592766</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575564</v>
+        <v>575425</v>
       </c>
       <c r="R12" t="n">
-        <v>6373780</v>
+        <v>6373803</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,57 +1941,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592766</v>
+        <v>128590113</v>
       </c>
       <c r="B13" t="n">
-        <v>57714</v>
+        <v>79648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575425</v>
+        <v>575564</v>
       </c>
       <c r="R13" t="n">
-        <v>6373803</v>
+        <v>6373780</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,7 +2051,7 @@
         <v>128593782</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>575415</v>
       </c>
       <c r="R14" t="n">
-        <v>6373845</v>
+        <v>6373844</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2164,53 +2164,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B15" t="n">
-        <v>58397</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R15" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,69 +2268,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>58400</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R16" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128591846</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>128589508</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>128593153</v>
       </c>
       <c r="B20" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2834,57 +2834,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128594789</v>
+        <v>128591716</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>95957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575404</v>
+        <v>575425</v>
       </c>
       <c r="R21" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,48 +2941,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128591716</v>
+        <v>128591743</v>
       </c>
       <c r="B22" t="n">
-        <v>95950</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575425</v>
+        <v>575392</v>
       </c>
       <c r="R22" t="n">
-        <v>6373803</v>
+        <v>6373787</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3021,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,22 +3036,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128593719</v>
+        <v>128591105</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,27 +3078,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575407</v>
+        <v>575470</v>
       </c>
       <c r="R23" t="n">
-        <v>6373854</v>
+        <v>6373770</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3136,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,22 +3147,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128594429</v>
+        <v>128593719</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3203,7 +3189,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3217,13 +3203,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575431</v>
+        <v>575407</v>
       </c>
       <c r="R24" t="n">
-        <v>6373926</v>
+        <v>6373854</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,10 +3275,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591743</v>
+        <v>128594429</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,20 +3303,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575392</v>
+        <v>575431</v>
       </c>
       <c r="R25" t="n">
-        <v>6373787</v>
+        <v>6373926</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3364,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,10 +3391,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591105</v>
+        <v>128594789</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3421,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575470</v>
+        <v>575404</v>
       </c>
       <c r="R26" t="n">
-        <v>6373770</v>
+        <v>6373845</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3507,57 +3507,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R27" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3586,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3596,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3623,53 +3619,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>57714</v>
+        <v>98643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R28" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3735,48 +3735,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128594305</v>
+        <v>128591928</v>
       </c>
       <c r="B29" t="n">
-        <v>91528</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575490</v>
+        <v>575385</v>
       </c>
       <c r="R29" t="n">
-        <v>6373927</v>
+        <v>6373791</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3805,7 +3814,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3815,7 +3824,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,69 +3839,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128591928</v>
+        <v>128594305</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>91533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575385</v>
+        <v>575490</v>
       </c>
       <c r="R30" t="n">
-        <v>6373791</v>
+        <v>6373927</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,57 +3946,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R31" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,50 +4070,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>57717</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R32" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>128593282</v>
       </c>
       <c r="B35" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>128594570</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>128594351</v>
       </c>
       <c r="B38" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>128591526</v>
       </c>
       <c r="B39" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>128594618</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>128593762</v>
       </c>
       <c r="B42" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128592340</v>
+        <v>128594506</v>
       </c>
       <c r="B43" t="n">
-        <v>57717</v>
+        <v>79648</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5309,42 +5309,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575425</v>
+        <v>575410</v>
       </c>
       <c r="R43" t="n">
-        <v>6373803</v>
+        <v>6373926</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5410,10 +5405,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128594506</v>
+        <v>128594384</v>
       </c>
       <c r="B44" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5445,10 +5440,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575410</v>
+        <v>575490</v>
       </c>
       <c r="R44" t="n">
-        <v>6373926</v>
+        <v>6373927</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5517,10 +5512,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128594384</v>
+        <v>128592340</v>
       </c>
       <c r="B45" t="n">
-        <v>79743</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,37 +5523,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575490</v>
+        <v>575425</v>
       </c>
       <c r="R45" t="n">
-        <v>6373927</v>
+        <v>6373803</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>79743</v>
+        <v>96239</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R48" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,32 +5973,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594598</v>
+        <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>96232</v>
+        <v>79648</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575422</v>
+        <v>575489</v>
       </c>
       <c r="R49" t="n">
-        <v>6373890</v>
+        <v>6373908</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6083,7 +6083,7 @@
         <v>128594164</v>
       </c>
       <c r="B50" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6192,54 +6192,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128594133</v>
+        <v>128593352</v>
       </c>
       <c r="B51" t="n">
-        <v>105699</v>
+        <v>79648</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575441</v>
+        <v>575401</v>
       </c>
       <c r="R51" t="n">
-        <v>6373840</v>
+        <v>6373862</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6308,45 +6299,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128593352</v>
+        <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>79743</v>
+        <v>105706</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575401</v>
+        <v>575441</v>
       </c>
       <c r="R52" t="n">
-        <v>6373862</v>
+        <v>6373840</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6415,38 +6415,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128589055</v>
+        <v>128594919</v>
       </c>
       <c r="B53" t="n">
-        <v>58090</v>
+        <v>98643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6455,13 +6459,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575467</v>
+        <v>575407</v>
       </c>
       <c r="R53" t="n">
-        <v>6373701</v>
+        <v>6373799</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6494,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6504,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6530,7 +6534,7 @@
         <v>128593763</v>
       </c>
       <c r="B54" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6643,42 +6647,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128594919</v>
+        <v>128589055</v>
       </c>
       <c r="B55" t="n">
-        <v>98636</v>
+        <v>58093</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575407</v>
+        <v>575467</v>
       </c>
       <c r="R55" t="n">
-        <v>6373799</v>
+        <v>6373701</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6762,7 +6762,7 @@
         <v>128593706</v>
       </c>
       <c r="B56" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B57" t="n">
-        <v>92798</v>
+        <v>43982</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,41 +6882,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6945,7 +6954,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6955,7 +6964,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6964,6 +6978,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6982,10 +6997,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>97507</v>
+        <v>92803</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,46 +7008,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,22 +7096,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B59" t="n">
-        <v>43980</v>
+        <v>97514</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7109,50 +7119,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R59" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7205,19 +7206,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7227,7 +7227,7 @@
         <v>128592034</v>
       </c>
       <c r="B60" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>128740640</v>
       </c>
       <c r="B63" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>128739848</v>
       </c>
       <c r="B64" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,24 +1405,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R8" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B9" t="n">
-        <v>91535</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1521,19 +1516,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R9" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,7 +1721,7 @@
         <v>128534744</v>
       </c>
       <c r="B11" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,48 +1825,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128590113</v>
+        <v>128593782</v>
       </c>
       <c r="B12" t="n">
-        <v>79648</v>
+        <v>98651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575564</v>
+        <v>575415</v>
       </c>
       <c r="R12" t="n">
-        <v>6373780</v>
+        <v>6373845</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,12 +1929,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2048,57 +2057,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128593782</v>
+        <v>128590113</v>
       </c>
       <c r="B14" t="n">
-        <v>98646</v>
+        <v>79653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575415</v>
+        <v>575564</v>
       </c>
       <c r="R14" t="n">
-        <v>6373844</v>
+        <v>6373780</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,12 +2152,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
         <v>128594706</v>
       </c>
       <c r="B15" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96928</v>
+        <v>96933</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2834,45 +2834,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128591716</v>
+        <v>128591105</v>
       </c>
       <c r="B21" t="n">
-        <v>95960</v>
+        <v>98651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575470</v>
       </c>
       <c r="R21" t="n">
-        <v>6373803</v>
+        <v>6373770</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2948,7 @@
         <v>128593719</v>
       </c>
       <c r="B22" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,10 +3061,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594429</v>
+        <v>128591743</v>
       </c>
       <c r="B23" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,29 +3089,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575431</v>
+        <v>575392</v>
       </c>
       <c r="R23" t="n">
-        <v>6373926</v>
+        <v>6373787</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3136,7 +3131,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3141,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,7 +3171,7 @@
         <v>128594789</v>
       </c>
       <c r="B24" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591743</v>
+        <v>128594429</v>
       </c>
       <c r="B25" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,20 +3312,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575392</v>
+        <v>575431</v>
       </c>
       <c r="R25" t="n">
-        <v>6373787</v>
+        <v>6373926</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,7 +3363,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3373,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,49 +3400,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591105</v>
+        <v>128591716</v>
       </c>
       <c r="B26" t="n">
-        <v>98646</v>
+        <v>95965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575470</v>
+        <v>575425</v>
       </c>
       <c r="R26" t="n">
-        <v>6373770</v>
+        <v>6373803</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3622,7 +3622,7 @@
         <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>91535</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128592258</v>
       </c>
       <c r="B31" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>128594570</v>
       </c>
       <c r="B36" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>128594506</v>
       </c>
       <c r="B41" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>128594384</v>
       </c>
       <c r="B42" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128593944</v>
       </c>
       <c r="B46" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594598</v>
+        <v>128594199</v>
       </c>
       <c r="B48" t="n">
-        <v>96242</v>
+        <v>79653</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575422</v>
+        <v>575489</v>
       </c>
       <c r="R48" t="n">
-        <v>6373890</v>
+        <v>6373908</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,45 +5973,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594199</v>
+        <v>128594164</v>
       </c>
       <c r="B49" t="n">
-        <v>79648</v>
+        <v>56913</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575489</v>
+        <v>575441</v>
       </c>
       <c r="R49" t="n">
-        <v>6373908</v>
+        <v>6373840</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6054,6 +6054,11 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6080,10 +6085,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594164</v>
+        <v>128594598</v>
       </c>
       <c r="B50" t="n">
-        <v>56913</v>
+        <v>96247</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6091,34 +6096,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575441</v>
+        <v>575422</v>
       </c>
       <c r="R50" t="n">
-        <v>6373840</v>
+        <v>6373890</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6161,11 +6166,6 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6195,7 +6195,7 @@
         <v>128593352</v>
       </c>
       <c r="B51" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R53" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,38 +6527,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128589055</v>
+        <v>128594919</v>
       </c>
       <c r="B54" t="n">
-        <v>58093</v>
+        <v>98651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6567,13 +6571,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575467</v>
+        <v>575407</v>
       </c>
       <c r="R54" t="n">
-        <v>6373701</v>
+        <v>6373799</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6606,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6616,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6639,10 +6643,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128594919</v>
+        <v>128593763</v>
       </c>
       <c r="B55" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6672,24 +6676,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575407</v>
+        <v>575376</v>
       </c>
       <c r="R55" t="n">
-        <v>6373799</v>
+        <v>6373829</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,7 +6722,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6728,7 +6732,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6743,69 +6747,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128593763</v>
+        <v>128593706</v>
       </c>
       <c r="B56" t="n">
-        <v>98646</v>
+        <v>57720</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575376</v>
+        <v>575366</v>
       </c>
       <c r="R56" t="n">
-        <v>6373829</v>
+        <v>6373838</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,22 +6859,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128594457</v>
+        <v>128593162</v>
       </c>
       <c r="B57" t="n">
-        <v>92806</v>
+        <v>97522</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,41 +6882,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575490</v>
+        <v>575378</v>
       </c>
       <c r="R57" t="n">
-        <v>6373927</v>
+        <v>6373836</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6945,7 +6950,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6955,7 +6960,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6970,22 +6975,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128593162</v>
+        <v>128601004</v>
       </c>
       <c r="B58" t="n">
-        <v>97517</v>
+        <v>43982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,46 +6998,50 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>6373836</v>
+        <v>6373840</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7070,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7080,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7080,28 +7094,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128601004</v>
+        <v>128594457</v>
       </c>
       <c r="B59" t="n">
-        <v>43982</v>
+        <v>92811</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7109,50 +7124,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101735</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575418</v>
+        <v>575490</v>
       </c>
       <c r="R59" t="n">
-        <v>6373840</v>
+        <v>6373927</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7205,7 +7206,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,19 +1405,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R8" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,24 +1521,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R9" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1825,57 +1825,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128593782</v>
+        <v>128590113</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>79653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575415</v>
+        <v>575564</v>
       </c>
       <c r="R12" t="n">
-        <v>6373845</v>
+        <v>6373780</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,69 +1920,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592766</v>
+        <v>128593782</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>98651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575425</v>
+        <v>575415</v>
       </c>
       <c r="R13" t="n">
-        <v>6373803</v>
+        <v>6373844</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2020,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,60 +2036,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128590113</v>
+        <v>128592766</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>57717</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575564</v>
+        <v>575425</v>
       </c>
       <c r="R14" t="n">
-        <v>6373780</v>
+        <v>6373803</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,57 +2164,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>58400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R15" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,65 +2264,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>58400</v>
+        <v>98651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R16" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128591105</v>
+        <v>128593719</v>
       </c>
       <c r="B21" t="n">
         <v>98651</v>
@@ -2864,22 +2864,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575470</v>
+        <v>575407</v>
       </c>
       <c r="R21" t="n">
-        <v>6373770</v>
+        <v>6373854</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,19 +2938,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128593719</v>
+        <v>128594429</v>
       </c>
       <c r="B22" t="n">
         <v>98651</v>
@@ -2975,7 +2980,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2989,13 +2994,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575407</v>
+        <v>575431</v>
       </c>
       <c r="R22" t="n">
-        <v>6373854</v>
+        <v>6373926</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3024,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,7 +3066,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128591743</v>
+        <v>128594789</v>
       </c>
       <c r="B23" t="n">
         <v>98651</v>
@@ -3089,20 +3094,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575392</v>
+        <v>575404</v>
       </c>
       <c r="R23" t="n">
-        <v>6373787</v>
+        <v>6373845</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,19 +3170,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128594789</v>
+        <v>128591743</v>
       </c>
       <c r="B24" t="n">
         <v>98651</v>
@@ -3196,29 +3210,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575404</v>
+        <v>575392</v>
       </c>
       <c r="R24" t="n">
-        <v>6373845</v>
+        <v>6373787</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3247,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3272,19 +3277,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128594429</v>
+        <v>128591105</v>
       </c>
       <c r="B25" t="n">
         <v>98651</v>
@@ -3314,27 +3319,22 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575431</v>
+        <v>575470</v>
       </c>
       <c r="R25" t="n">
-        <v>6373926</v>
+        <v>6373770</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,12 +3388,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3507,53 +3507,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B27" t="n">
-        <v>57717</v>
+        <v>98651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R27" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3596,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,57 +3623,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>57717</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R28" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,45 +3958,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R31" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,50 +4070,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>98651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R32" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5866,32 +5866,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128594199</v>
+        <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>79653</v>
+        <v>96247</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575489</v>
+        <v>575422</v>
       </c>
       <c r="R48" t="n">
-        <v>6373908</v>
+        <v>6373890</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5973,45 +5973,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128594164</v>
+        <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>56913</v>
+        <v>79653</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575441</v>
+        <v>575489</v>
       </c>
       <c r="R49" t="n">
-        <v>6373840</v>
+        <v>6373908</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6054,11 +6054,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6085,10 +6080,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128594598</v>
+        <v>128594164</v>
       </c>
       <c r="B50" t="n">
-        <v>96247</v>
+        <v>56913</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6096,34 +6091,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575422</v>
+        <v>575441</v>
       </c>
       <c r="R50" t="n">
-        <v>6373890</v>
+        <v>6373840</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6166,6 +6161,11 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tjäderhöna sandbadplats vid rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6192,45 +6192,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128593352</v>
+        <v>128594133</v>
       </c>
       <c r="B51" t="n">
-        <v>79653</v>
+        <v>105714</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575401</v>
+        <v>575441</v>
       </c>
       <c r="R51" t="n">
-        <v>6373862</v>
+        <v>6373840</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6299,54 +6308,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128594133</v>
+        <v>128593352</v>
       </c>
       <c r="B52" t="n">
-        <v>105714</v>
+        <v>79653</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575441</v>
+        <v>575401</v>
       </c>
       <c r="R52" t="n">
-        <v>6373840</v>
+        <v>6373862</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128589055</v>
+        <v>128593706</v>
       </c>
       <c r="B53" t="n">
-        <v>58093</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575467</v>
+        <v>575366</v>
       </c>
       <c r="R53" t="n">
-        <v>6373701</v>
+        <v>6373838</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,42 +6527,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128594919</v>
+        <v>128589055</v>
       </c>
       <c r="B54" t="n">
-        <v>98651</v>
+        <v>58093</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6571,13 +6567,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575407</v>
+        <v>575467</v>
       </c>
       <c r="R54" t="n">
-        <v>6373799</v>
+        <v>6373701</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6606,7 +6602,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6616,7 +6612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6643,7 +6639,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128593763</v>
+        <v>128594919</v>
       </c>
       <c r="B55" t="n">
         <v>98651</v>
@@ -6676,24 +6672,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575376</v>
+        <v>575407</v>
       </c>
       <c r="R55" t="n">
-        <v>6373829</v>
+        <v>6373799</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6722,7 +6718,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6732,7 +6728,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6747,65 +6743,69 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128593706</v>
+        <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>57720</v>
+        <v>98651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575366</v>
+        <v>575376</v>
       </c>
       <c r="R56" t="n">
-        <v>6373838</v>
+        <v>6373829</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,12 +6859,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128601004</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>43982</v>
+        <v>92811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6998,50 +6998,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101735</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373840</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7070,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7080,12 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7094,7 +7080,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7113,10 +7098,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B59" t="n">
-        <v>92811</v>
+        <v>43982</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7124,41 +7109,50 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R59" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7191,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7206,6 +7205,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7224,38 +7224,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B60" t="n">
-        <v>57720</v>
+        <v>98651</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7264,10 +7268,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R60" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7299,7 +7303,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7336,42 +7340,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B61" t="n">
-        <v>98651</v>
+        <v>57720</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R61" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534608</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128534306</v>
       </c>
       <c r="B7" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533348</v>
+        <v>128534916</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>91546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,24 +1405,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575351</v>
+        <v>575310</v>
       </c>
       <c r="R8" t="n">
-        <v>6373811</v>
+        <v>6373895</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128534916</v>
+        <v>128533348</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1521,19 +1516,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575310</v>
+        <v>575351</v>
       </c>
       <c r="R9" t="n">
-        <v>6373895</v>
+        <v>6373811</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,7 +1721,7 @@
         <v>128534744</v>
       </c>
       <c r="B11" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128590113</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128593782</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>575415</v>
       </c>
       <c r="R13" t="n">
-        <v>6373844</v>
+        <v>6373845</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2164,53 +2164,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B15" t="n">
-        <v>58400</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R15" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,69 +2268,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>58400</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R16" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>128593449</v>
       </c>
       <c r="B17" t="n">
-        <v>96933</v>
+        <v>96941</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>128593153</v>
       </c>
       <c r="B18" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2834,57 +2834,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128593719</v>
+        <v>128591716</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>95973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575407</v>
+        <v>575425</v>
       </c>
       <c r="R21" t="n">
-        <v>6373854</v>
+        <v>6373803</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2913,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2929,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128594429</v>
+        <v>128591105</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,27 +2971,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575431</v>
+        <v>575470</v>
       </c>
       <c r="R22" t="n">
-        <v>6373926</v>
+        <v>6373770</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3029,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,22 +3040,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128594789</v>
+        <v>128593719</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,24 +3085,24 @@
           <t>15</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575404</v>
+        <v>575407</v>
       </c>
       <c r="R23" t="n">
-        <v>6373845</v>
+        <v>6373854</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3145,7 +3131,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3141,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,12 +3156,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3185,7 +3171,7 @@
         <v>128591743</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,10 +3275,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591105</v>
+        <v>128594789</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3319,7 +3305,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3328,13 +3319,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575470</v>
+        <v>575404</v>
       </c>
       <c r="R25" t="n">
-        <v>6373770</v>
+        <v>6373845</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3400,48 +3391,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591716</v>
+        <v>128594429</v>
       </c>
       <c r="B26" t="n">
-        <v>95965</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575425</v>
+        <v>575431</v>
       </c>
       <c r="R26" t="n">
-        <v>6373803</v>
+        <v>6373926</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,69 +3495,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>57717</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R27" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3586,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3596,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3623,53 +3619,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B28" t="n">
-        <v>57717</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R28" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,7 +3738,7 @@
         <v>128594305</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91546</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>128591928</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128592258</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>128594142</v>
       </c>
       <c r="B33" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>128593346</v>
       </c>
       <c r="B34" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,53 +4391,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R35" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4466,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4480,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,69 +4495,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R36" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
         <v>128593383</v>
       </c>
       <c r="B37" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>128591200</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>128594506</v>
       </c>
       <c r="B41" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>128594384</v>
       </c>
       <c r="B42" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>128594618</v>
       </c>
       <c r="B44" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>128593762</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,57 +5624,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128593944</v>
+        <v>128600928</v>
       </c>
       <c r="B46" t="n">
-        <v>98651</v>
+        <v>5362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>101728</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575453</v>
+        <v>575524</v>
       </c>
       <c r="R46" t="n">
-        <v>6373840</v>
+        <v>6373718</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5703,7 +5707,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5713,7 +5717,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fanns på en liggande grov asplåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,79 +5731,76 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128600928</v>
+        <v>128593944</v>
       </c>
       <c r="B47" t="n">
-        <v>5362</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575524</v>
+        <v>575453</v>
       </c>
       <c r="R47" t="n">
-        <v>6373718</v>
+        <v>6373840</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5823,7 +5829,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5833,12 +5839,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fanns på en liggande grov asplåga</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,19 +5848,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5869,7 +5869,7 @@
         <v>128594598</v>
       </c>
       <c r="B48" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>128594199</v>
       </c>
       <c r="B49" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,54 +6192,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128594133</v>
+        <v>128593352</v>
       </c>
       <c r="B51" t="n">
-        <v>105714</v>
+        <v>79654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575441</v>
+        <v>575401</v>
       </c>
       <c r="R51" t="n">
-        <v>6373840</v>
+        <v>6373862</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6308,45 +6299,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128593352</v>
+        <v>128594133</v>
       </c>
       <c r="B52" t="n">
-        <v>79653</v>
+        <v>105722</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575401</v>
+        <v>575441</v>
       </c>
       <c r="R52" t="n">
-        <v>6373862</v>
+        <v>6373840</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6642,7 +6642,7 @@
         <v>128594919</v>
       </c>
       <c r="B55" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128593763</v>
       </c>
       <c r="B56" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>97522</v>
+        <v>92819</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,46 +6882,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R57" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6950,7 +6945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6955,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6975,22 +6970,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128594457</v>
+        <v>128593162</v>
       </c>
       <c r="B58" t="n">
-        <v>92811</v>
+        <v>97530</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6998,41 +6993,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575490</v>
+        <v>575378</v>
       </c>
       <c r="R58" t="n">
-        <v>6373927</v>
+        <v>6373836</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,12 +7086,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7227,7 +7227,7 @@
         <v>128592019</v>
       </c>
       <c r="B60" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128591846</v>
+        <v>128589508</v>
       </c>
       <c r="B19" t="n">
         <v>57720</v>
@@ -2634,7 +2634,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2642,17 +2646,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575382</v>
+        <v>575483</v>
       </c>
       <c r="R19" t="n">
-        <v>6373783</v>
+        <v>6373688</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2695,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,19 +2710,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128589508</v>
+        <v>128591846</v>
       </c>
       <c r="B20" t="n">
         <v>57720</v>
@@ -2746,11 +2750,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2758,17 +2758,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575483</v>
+        <v>575382</v>
       </c>
       <c r="R20" t="n">
-        <v>6373688</v>
+        <v>6373783</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,12 +2822,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -5075,48 +5075,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128594506</v>
+        <v>128594618</v>
       </c>
       <c r="B41" t="n">
-        <v>79654</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575410</v>
+        <v>575433</v>
       </c>
       <c r="R41" t="n">
-        <v>6373926</v>
+        <v>6373862</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,60 +5170,69 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128594384</v>
+        <v>128593762</v>
       </c>
       <c r="B42" t="n">
-        <v>79654</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575490</v>
+        <v>575411</v>
       </c>
       <c r="R42" t="n">
-        <v>6373927</v>
+        <v>6373848</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5252,7 +5261,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5271,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5277,22 +5286,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128592340</v>
+        <v>128594506</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,42 +5309,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575425</v>
+        <v>575410</v>
       </c>
       <c r="R43" t="n">
-        <v>6373803</v>
+        <v>6373926</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5401,48 +5405,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128594618</v>
+        <v>128594384</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>79654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575433</v>
+        <v>575490</v>
       </c>
       <c r="R44" t="n">
-        <v>6373862</v>
+        <v>6373927</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5471,7 +5475,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5481,7 +5485,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,69 +5500,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128593762</v>
+        <v>128592340</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575411</v>
+        <v>575425</v>
       </c>
       <c r="R45" t="n">
-        <v>6373848</v>
+        <v>6373803</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6415,27 +6415,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6446,22 +6446,22 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R53" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,38 +6527,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128589055</v>
+        <v>128594919</v>
       </c>
       <c r="B54" t="n">
-        <v>58093</v>
+        <v>98659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6567,13 +6571,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575467</v>
+        <v>575407</v>
       </c>
       <c r="R54" t="n">
-        <v>6373701</v>
+        <v>6373799</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6602,7 +6606,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6616,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6639,7 +6643,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128594919</v>
+        <v>128593763</v>
       </c>
       <c r="B55" t="n">
         <v>98659</v>
@@ -6672,24 +6676,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575407</v>
+        <v>575376</v>
       </c>
       <c r="R55" t="n">
-        <v>6373799</v>
+        <v>6373829</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,7 +6722,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6728,7 +6732,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6743,69 +6747,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128593763</v>
+        <v>128593706</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575376</v>
+        <v>575366</v>
       </c>
       <c r="R56" t="n">
-        <v>6373829</v>
+        <v>6373838</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,22 +6859,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B57" t="n">
-        <v>92819</v>
+        <v>43982</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,41 +6882,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6945,7 +6954,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6955,7 +6964,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6964,6 +6978,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6982,10 +6997,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128593162</v>
+        <v>128594457</v>
       </c>
       <c r="B58" t="n">
-        <v>97530</v>
+        <v>92819</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,46 +7008,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575378</v>
+        <v>575490</v>
       </c>
       <c r="R58" t="n">
-        <v>6373836</v>
+        <v>6373927</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7061,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,22 +7096,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128601004</v>
+        <v>128593162</v>
       </c>
       <c r="B59" t="n">
-        <v>43982</v>
+        <v>97530</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7109,50 +7119,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R59" t="n">
-        <v>6373840</v>
+        <v>6373836</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7205,19 +7206,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -1825,48 +1825,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128590113</v>
+        <v>128593782</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575564</v>
+        <v>575415</v>
       </c>
       <c r="R12" t="n">
-        <v>6373780</v>
+        <v>6373845</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,69 +1929,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128593782</v>
+        <v>128592766</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575415</v>
+        <v>575425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373845</v>
+        <v>6373803</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,69 +2045,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592766</v>
+        <v>128590113</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575425</v>
+        <v>575564</v>
       </c>
       <c r="R14" t="n">
-        <v>6373803</v>
+        <v>6373780</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,57 +2164,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128594706</v>
+        <v>128593286</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>58400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575431</v>
+        <v>575401</v>
       </c>
       <c r="R15" t="n">
-        <v>6373860</v>
+        <v>6373830</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,65 +2264,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128593286</v>
+        <v>128594706</v>
       </c>
       <c r="B16" t="n">
-        <v>58400</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575401</v>
+        <v>575431</v>
       </c>
       <c r="R16" t="n">
-        <v>6373830</v>
+        <v>6373860</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128589508</v>
+        <v>128591846</v>
       </c>
       <c r="B19" t="n">
         <v>57720</v>
@@ -2634,11 +2634,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2646,17 +2642,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575483</v>
+        <v>575382</v>
       </c>
       <c r="R19" t="n">
-        <v>6373688</v>
+        <v>6373783</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2685,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,19 +2706,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128591846</v>
+        <v>128589508</v>
       </c>
       <c r="B20" t="n">
         <v>57720</v>
@@ -2750,7 +2746,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2758,17 +2758,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575382</v>
+        <v>575483</v>
       </c>
       <c r="R20" t="n">
-        <v>6373783</v>
+        <v>6373688</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,60 +2822,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128591716</v>
+        <v>128593719</v>
       </c>
       <c r="B21" t="n">
-        <v>95973</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575407</v>
       </c>
       <c r="R21" t="n">
-        <v>6373803</v>
+        <v>6373854</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,19 +2938,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128591105</v>
+        <v>128594429</v>
       </c>
       <c r="B22" t="n">
         <v>98659</v>
@@ -2971,22 +2980,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575470</v>
+        <v>575431</v>
       </c>
       <c r="R22" t="n">
-        <v>6373770</v>
+        <v>6373926</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3015,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,19 +3054,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128593719</v>
+        <v>128594789</v>
       </c>
       <c r="B23" t="n">
         <v>98659</v>
@@ -3085,24 +3099,24 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575407</v>
+        <v>575404</v>
       </c>
       <c r="R23" t="n">
-        <v>6373854</v>
+        <v>6373845</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,12 +3170,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3275,7 +3289,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128594789</v>
+        <v>128591105</v>
       </c>
       <c r="B25" t="n">
         <v>98659</v>
@@ -3305,12 +3319,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3319,13 +3328,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575404</v>
+        <v>575470</v>
       </c>
       <c r="R25" t="n">
-        <v>6373845</v>
+        <v>6373770</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3391,57 +3400,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128594429</v>
+        <v>128591716</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>95973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575431</v>
+        <v>575425</v>
       </c>
       <c r="R26" t="n">
-        <v>6373926</v>
+        <v>6373803</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,65 +3495,69 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128593463</v>
+        <v>128591348</v>
       </c>
       <c r="B27" t="n">
-        <v>57717</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575366</v>
+        <v>575424</v>
       </c>
       <c r="R27" t="n">
-        <v>6373838</v>
+        <v>6373785</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3596,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,57 +3623,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128591348</v>
+        <v>128593463</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>57717</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575424</v>
+        <v>575366</v>
       </c>
       <c r="R28" t="n">
-        <v>6373785</v>
+        <v>6373838</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,50 +3958,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128594827</v>
+        <v>128592258</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575432</v>
+        <v>575408</v>
       </c>
       <c r="R31" t="n">
-        <v>6373861</v>
+        <v>6373794</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4033,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,45 +4065,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128592258</v>
+        <v>128594827</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575408</v>
+        <v>575432</v>
       </c>
       <c r="R32" t="n">
-        <v>6373794</v>
+        <v>6373861</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,7 +4177,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128594142</v>
+        <v>128593346</v>
       </c>
       <c r="B33" t="n">
         <v>96255</v>
@@ -4208,14 +4208,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575505</v>
+        <v>575354</v>
       </c>
       <c r="R33" t="n">
-        <v>6373862</v>
+        <v>6373840</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,7 +4284,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128593346</v>
+        <v>128594142</v>
       </c>
       <c r="B34" t="n">
         <v>96255</v>
@@ -4315,14 +4315,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575354</v>
+        <v>575505</v>
       </c>
       <c r="R34" t="n">
-        <v>6373840</v>
+        <v>6373862</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,57 +4391,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128594570</v>
+        <v>128593282</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575410</v>
+        <v>575357</v>
       </c>
       <c r="R35" t="n">
-        <v>6373926</v>
+        <v>6373830</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4470,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,65 +4491,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128593282</v>
+        <v>128594570</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575357</v>
+        <v>575410</v>
       </c>
       <c r="R36" t="n">
-        <v>6373830</v>
+        <v>6373926</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,12 +4607,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6415,38 +6415,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128589055</v>
+        <v>128594919</v>
       </c>
       <c r="B53" t="n">
-        <v>58093</v>
+        <v>98659</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6455,13 +6459,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575467</v>
+        <v>575407</v>
       </c>
       <c r="R53" t="n">
-        <v>6373701</v>
+        <v>6373799</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,7 +6494,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6504,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,7 +6531,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128594919</v>
+        <v>128593763</v>
       </c>
       <c r="B54" t="n">
         <v>98659</v>
@@ -6560,24 +6564,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575407</v>
+        <v>575376</v>
       </c>
       <c r="R54" t="n">
-        <v>6373799</v>
+        <v>6373829</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6606,7 +6610,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6616,7 +6620,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6631,69 +6635,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128593763</v>
+        <v>128593706</v>
       </c>
       <c r="B55" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Pilebo, Pilebo, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575376</v>
+        <v>575366</v>
       </c>
       <c r="R55" t="n">
-        <v>6373829</v>
+        <v>6373838</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6747,39 +6747,39 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128593706</v>
+        <v>128589055</v>
       </c>
       <c r="B56" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6790,22 +6790,22 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Pilebo, Pilebo, Sm</t>
+          <t>Fagerdalskärr, Fagerdalskärr, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575366</v>
+        <v>575467</v>
       </c>
       <c r="R56" t="n">
-        <v>6373838</v>
+        <v>6373701</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128601004</v>
+        <v>128594457</v>
       </c>
       <c r="B57" t="n">
-        <v>43982</v>
+        <v>92819</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6882,50 +6882,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101735</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagerkärr, Juxtorp, Sm</t>
+          <t>Fagerkärr, Fagerkärr, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575490</v>
       </c>
       <c r="R57" t="n">
-        <v>6373840</v>
+        <v>6373927</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6954,7 +6945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6964,12 +6955,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fanns på en högstubbe av björk och fnösketicka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,7 +6964,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6997,10 +6982,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128594457</v>
+        <v>128601004</v>
       </c>
       <c r="B58" t="n">
-        <v>92819</v>
+        <v>43982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7008,41 +6993,50 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerkärr, Fagerkärr, Sm</t>
+          <t>Fagerkärr, Juxtorp, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575490</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>6373927</v>
+        <v>6373840</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7071,7 +7065,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7075,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fanns på en högstubbe av björk och fnösketicka</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7090,6 +7089,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7224,42 +7224,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128592019</v>
+        <v>128592034</v>
       </c>
       <c r="B60" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7268,10 +7264,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575390</v>
+        <v>575392</v>
       </c>
       <c r="R60" t="n">
-        <v>6373794</v>
+        <v>6373790</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7303,7 +7299,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7309,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7340,38 +7336,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128592034</v>
+        <v>128592019</v>
       </c>
       <c r="B61" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575392</v>
+        <v>575390</v>
       </c>
       <c r="R61" t="n">
-        <v>6373790</v>
+        <v>6373794</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>128740640</v>
       </c>
       <c r="B63" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>128739848</v>
       </c>
       <c r="B64" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -7455,7 +7455,7 @@
         <v>128741110</v>
       </c>
       <c r="B62" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>128740640</v>
       </c>
       <c r="B63" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>128739848</v>
       </c>
       <c r="B64" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>128740165</v>
       </c>
       <c r="B65" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>128741243</v>
       </c>
       <c r="B66" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>128741002</v>
       </c>
       <c r="B67" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>128740282</v>
       </c>
       <c r="B68" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128739569</v>
       </c>
       <c r="B69" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>128740227</v>
       </c>
       <c r="B70" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 36932-2025 artfynd.xlsx
+++ b/artfynd/A 36932-2025 artfynd.xlsx
@@ -8491,7 +8491,7 @@
         <v>128740331</v>
       </c>
       <c r="B71" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
